--- a/OUTPUT.xlsx
+++ b/OUTPUT.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Output_1a" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Output_1b" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Output_2a" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Output_2b" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,11 +19,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="€#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;€&quot;+#,##0.00;&quot;€&quot;-#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0;-#,##0"/>
+    <numFmt numFmtId="168" formatCode="&quot;+€&quot;#,##0.00;&quot;-€&quot;#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="&quot;+&quot;0.0;&quot;- &quot;0.0"/>
+    <numFmt numFmtId="171" formatCode="&quot;+&quot;0.00;&quot;- &quot;0.00"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -350,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -509,6 +515,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="27" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5209,4 +5251,5605 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="5.5" customWidth="1" min="3" max="3"/>
+    <col width="5.5" customWidth="1" min="4" max="4"/>
+    <col width="5.5" customWidth="1" min="5" max="5"/>
+    <col width="5.5" customWidth="1" min="6" max="6"/>
+    <col width="5.5" customWidth="1" min="7" max="7"/>
+    <col width="5.5" customWidth="1" min="8" max="8"/>
+    <col width="5.5" customWidth="1" min="9" max="9"/>
+    <col width="5.5" customWidth="1" min="10" max="10"/>
+    <col width="5.5" customWidth="1" min="11" max="11"/>
+    <col width="5.5" customWidth="1" min="12" max="12"/>
+    <col width="5.5" customWidth="1" min="13" max="13"/>
+    <col width="5.5" customWidth="1" min="14" max="14"/>
+    <col width="5.5" customWidth="1" min="15" max="15"/>
+    <col width="5.5" customWidth="1" min="16" max="16"/>
+    <col width="5.5" customWidth="1" min="17" max="17"/>
+    <col width="5.5" customWidth="1" min="18" max="18"/>
+    <col width="5.5" customWidth="1" min="19" max="19"/>
+    <col width="5.5" customWidth="1" min="20" max="20"/>
+    <col width="5.5" customWidth="1" min="21" max="21"/>
+    <col width="5.5" customWidth="1" min="22" max="22"/>
+    <col width="5.5" customWidth="1" min="23" max="23"/>
+    <col width="5.5" customWidth="1" min="24" max="24"/>
+    <col width="5.5" customWidth="1" min="25" max="25"/>
+    <col width="5.5" customWidth="1" min="26" max="26"/>
+    <col width="5.5" customWidth="1" min="27" max="27"/>
+    <col width="5.5" customWidth="1" min="28" max="28"/>
+    <col width="5.5" customWidth="1" min="29" max="29"/>
+    <col width="5.5" customWidth="1" min="30" max="30"/>
+    <col width="5.5" customWidth="1" min="31" max="31"/>
+    <col width="5.5" customWidth="1" min="32" max="32"/>
+    <col width="5.5" customWidth="1" min="33" max="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="37" t="inlineStr">
+        <is>
+          <t>Assignment 2a - Optimal solution (finite capacity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1"/>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>Total cost</t>
+        </is>
+      </c>
+      <c r="C3" s="39" t="n">
+        <v>540488.8</v>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>Setup cost</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="n">
+        <v>145500</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>Holding cost</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="n">
+        <v>394988.8</v>
+      </c>
+    </row>
+    <row r="6" ht="4" customHeight="1"/>
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>Workstation X capacity</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>800 units / week</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>Workstation Y capacity</t>
+        </is>
+      </c>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>10000 min / week  (3 min/B1401, 2 min/B2302)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>Production / order schedule (units)</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="42" t="n"/>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="42" t="n"/>
+      <c r="H10" s="42" t="n"/>
+      <c r="I10" s="42" t="n"/>
+      <c r="J10" s="42" t="n"/>
+      <c r="K10" s="42" t="n"/>
+      <c r="L10" s="42" t="n"/>
+      <c r="M10" s="42" t="n"/>
+      <c r="N10" s="42" t="n"/>
+      <c r="O10" s="42" t="n"/>
+      <c r="P10" s="42" t="n"/>
+      <c r="Q10" s="42" t="n"/>
+      <c r="R10" s="42" t="n"/>
+      <c r="S10" s="42" t="n"/>
+      <c r="T10" s="42" t="n"/>
+      <c r="U10" s="42" t="n"/>
+      <c r="V10" s="42" t="n"/>
+      <c r="W10" s="42" t="n"/>
+      <c r="X10" s="42" t="n"/>
+      <c r="Y10" s="42" t="n"/>
+      <c r="Z10" s="42" t="n"/>
+      <c r="AA10" s="42" t="n"/>
+      <c r="AB10" s="42" t="n"/>
+      <c r="AC10" s="42" t="n"/>
+      <c r="AD10" s="42" t="n"/>
+      <c r="AE10" s="42" t="n"/>
+      <c r="AF10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L11" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M11" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N11" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O11" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P11" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q11" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R11" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S11" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T11" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U11" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V11" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W11" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X11" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y11" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z11" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA11" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB11" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC11" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD11" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE11" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF11" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>B1401</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>3316</v>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="F12" s="46" t="inlineStr"/>
+      <c r="G12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="H12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="I12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="J12" s="46" t="inlineStr"/>
+      <c r="K12" s="46" t="inlineStr"/>
+      <c r="L12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="M12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="N12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="O12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="P12" s="46" t="inlineStr"/>
+      <c r="Q12" s="46" t="inlineStr"/>
+      <c r="R12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="S12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="T12" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="U12" s="46" t="inlineStr"/>
+      <c r="V12" s="46" t="inlineStr"/>
+      <c r="W12" s="46" t="inlineStr"/>
+      <c r="X12" s="46" t="inlineStr"/>
+      <c r="Y12" s="46" t="inlineStr"/>
+      <c r="Z12" s="46" t="inlineStr"/>
+      <c r="AA12" s="46" t="inlineStr"/>
+      <c r="AB12" s="46" t="inlineStr"/>
+      <c r="AC12" s="46" t="inlineStr"/>
+      <c r="AD12" s="46" t="inlineStr"/>
+      <c r="AE12" s="46" t="inlineStr"/>
+      <c r="AF12" s="46" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>B2302</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr"/>
+      <c r="D13" s="46" t="inlineStr"/>
+      <c r="E13" s="46" t="inlineStr"/>
+      <c r="F13" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G13" s="46" t="inlineStr"/>
+      <c r="H13" s="46" t="inlineStr"/>
+      <c r="I13" s="46" t="inlineStr"/>
+      <c r="J13" s="45" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K13" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L13" s="46" t="inlineStr"/>
+      <c r="M13" s="46" t="inlineStr"/>
+      <c r="N13" s="46" t="inlineStr"/>
+      <c r="O13" s="46" t="inlineStr"/>
+      <c r="P13" s="45" t="n">
+        <v>4600</v>
+      </c>
+      <c r="Q13" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R13" s="46" t="inlineStr"/>
+      <c r="S13" s="46" t="inlineStr"/>
+      <c r="T13" s="46" t="inlineStr"/>
+      <c r="U13" s="45" t="n">
+        <v>4084</v>
+      </c>
+      <c r="V13" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W13" s="46" t="inlineStr"/>
+      <c r="X13" s="46" t="inlineStr"/>
+      <c r="Y13" s="46" t="inlineStr"/>
+      <c r="Z13" s="46" t="inlineStr"/>
+      <c r="AA13" s="46" t="inlineStr"/>
+      <c r="AB13" s="46" t="inlineStr"/>
+      <c r="AC13" s="46" t="inlineStr"/>
+      <c r="AD13" s="46" t="inlineStr"/>
+      <c r="AE13" s="46" t="inlineStr"/>
+      <c r="AF13" s="46" t="inlineStr"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>B3201</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr"/>
+      <c r="D14" s="46" t="inlineStr"/>
+      <c r="E14" s="46" t="inlineStr"/>
+      <c r="F14" s="46" t="inlineStr"/>
+      <c r="G14" s="46" t="inlineStr"/>
+      <c r="H14" s="45" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I14" s="46" t="inlineStr"/>
+      <c r="J14" s="46" t="inlineStr"/>
+      <c r="K14" s="46" t="inlineStr"/>
+      <c r="L14" s="46" t="inlineStr"/>
+      <c r="M14" s="45" t="n">
+        <v>4800</v>
+      </c>
+      <c r="N14" s="46" t="inlineStr"/>
+      <c r="O14" s="46" t="inlineStr"/>
+      <c r="P14" s="46" t="inlineStr"/>
+      <c r="Q14" s="46" t="inlineStr"/>
+      <c r="R14" s="46" t="inlineStr"/>
+      <c r="S14" s="45" t="n">
+        <v>4800</v>
+      </c>
+      <c r="T14" s="46" t="inlineStr"/>
+      <c r="U14" s="46" t="inlineStr"/>
+      <c r="V14" s="46" t="inlineStr"/>
+      <c r="W14" s="46" t="inlineStr"/>
+      <c r="X14" s="45" t="n">
+        <v>4542</v>
+      </c>
+      <c r="Y14" s="46" t="inlineStr"/>
+      <c r="Z14" s="46" t="inlineStr"/>
+      <c r="AA14" s="46" t="inlineStr"/>
+      <c r="AB14" s="46" t="inlineStr"/>
+      <c r="AC14" s="46" t="inlineStr"/>
+      <c r="AD14" s="46" t="inlineStr"/>
+      <c r="AE14" s="46" t="inlineStr"/>
+      <c r="AF14" s="46" t="inlineStr"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>B4702</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="n">
+        <v>13600</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>15750</v>
+      </c>
+      <c r="E15" s="46" t="inlineStr"/>
+      <c r="F15" s="46" t="inlineStr"/>
+      <c r="G15" s="46" t="inlineStr"/>
+      <c r="H15" s="46" t="inlineStr"/>
+      <c r="I15" s="45" t="n">
+        <v>16800</v>
+      </c>
+      <c r="J15" s="46" t="inlineStr"/>
+      <c r="K15" s="46" t="inlineStr"/>
+      <c r="L15" s="46" t="inlineStr"/>
+      <c r="M15" s="46" t="inlineStr"/>
+      <c r="N15" s="46" t="inlineStr"/>
+      <c r="O15" s="45" t="n">
+        <v>16800</v>
+      </c>
+      <c r="P15" s="46" t="inlineStr"/>
+      <c r="Q15" s="46" t="inlineStr"/>
+      <c r="R15" s="46" t="inlineStr"/>
+      <c r="S15" s="46" t="inlineStr"/>
+      <c r="T15" s="45" t="n">
+        <v>15897</v>
+      </c>
+      <c r="U15" s="46" t="inlineStr"/>
+      <c r="V15" s="46" t="inlineStr"/>
+      <c r="W15" s="46" t="inlineStr"/>
+      <c r="X15" s="46" t="inlineStr"/>
+      <c r="Y15" s="46" t="inlineStr"/>
+      <c r="Z15" s="46" t="inlineStr"/>
+      <c r="AA15" s="46" t="inlineStr"/>
+      <c r="AB15" s="46" t="inlineStr"/>
+      <c r="AC15" s="46" t="inlineStr"/>
+      <c r="AD15" s="46" t="inlineStr"/>
+      <c r="AE15" s="46" t="inlineStr"/>
+      <c r="AF15" s="46" t="inlineStr"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>V1501</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr"/>
+      <c r="D16" s="46" t="inlineStr"/>
+      <c r="E16" s="46" t="inlineStr"/>
+      <c r="F16" s="46" t="inlineStr"/>
+      <c r="G16" s="46" t="inlineStr"/>
+      <c r="H16" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I16" s="46" t="inlineStr"/>
+      <c r="J16" s="46" t="inlineStr"/>
+      <c r="K16" s="46" t="inlineStr"/>
+      <c r="L16" s="46" t="inlineStr"/>
+      <c r="M16" s="45" t="n">
+        <v>3200</v>
+      </c>
+      <c r="N16" s="46" t="inlineStr"/>
+      <c r="O16" s="46" t="inlineStr"/>
+      <c r="P16" s="46" t="inlineStr"/>
+      <c r="Q16" s="46" t="inlineStr"/>
+      <c r="R16" s="46" t="inlineStr"/>
+      <c r="S16" s="45" t="n">
+        <v>3200</v>
+      </c>
+      <c r="T16" s="46" t="inlineStr"/>
+      <c r="U16" s="46" t="inlineStr"/>
+      <c r="V16" s="46" t="inlineStr"/>
+      <c r="W16" s="46" t="inlineStr"/>
+      <c r="X16" s="45" t="n">
+        <v>3028</v>
+      </c>
+      <c r="Y16" s="46" t="inlineStr"/>
+      <c r="Z16" s="46" t="inlineStr"/>
+      <c r="AA16" s="46" t="inlineStr"/>
+      <c r="AB16" s="46" t="inlineStr"/>
+      <c r="AC16" s="46" t="inlineStr"/>
+      <c r="AD16" s="46" t="inlineStr"/>
+      <c r="AE16" s="46" t="inlineStr"/>
+      <c r="AF16" s="46" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>V6302</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr"/>
+      <c r="D17" s="46" t="inlineStr"/>
+      <c r="E17" s="46" t="inlineStr"/>
+      <c r="F17" s="46" t="inlineStr"/>
+      <c r="G17" s="46" t="inlineStr"/>
+      <c r="H17" s="45" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I17" s="45" t="n">
+        <v>2250</v>
+      </c>
+      <c r="J17" s="46" t="inlineStr"/>
+      <c r="K17" s="46" t="inlineStr"/>
+      <c r="L17" s="46" t="inlineStr"/>
+      <c r="M17" s="46" t="inlineStr"/>
+      <c r="N17" s="45" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O17" s="46" t="inlineStr"/>
+      <c r="P17" s="46" t="inlineStr"/>
+      <c r="Q17" s="46" t="inlineStr"/>
+      <c r="R17" s="46" t="inlineStr"/>
+      <c r="S17" s="46" t="inlineStr"/>
+      <c r="T17" s="45" t="n">
+        <v>2400</v>
+      </c>
+      <c r="U17" s="46" t="inlineStr"/>
+      <c r="V17" s="46" t="inlineStr"/>
+      <c r="W17" s="46" t="inlineStr"/>
+      <c r="X17" s="46" t="inlineStr"/>
+      <c r="Y17" s="45" t="n">
+        <v>2271</v>
+      </c>
+      <c r="Z17" s="46" t="inlineStr"/>
+      <c r="AA17" s="46" t="inlineStr"/>
+      <c r="AB17" s="46" t="inlineStr"/>
+      <c r="AC17" s="46" t="inlineStr"/>
+      <c r="AD17" s="46" t="inlineStr"/>
+      <c r="AE17" s="46" t="inlineStr"/>
+      <c r="AF17" s="46" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="n">
+        <v>650</v>
+      </c>
+      <c r="D18" s="46" t="inlineStr"/>
+      <c r="E18" s="46" t="inlineStr"/>
+      <c r="F18" s="46" t="inlineStr"/>
+      <c r="G18" s="46" t="inlineStr"/>
+      <c r="H18" s="46" t="inlineStr"/>
+      <c r="I18" s="46" t="inlineStr"/>
+      <c r="J18" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="K18" s="45" t="n">
+        <v>750</v>
+      </c>
+      <c r="L18" s="46" t="inlineStr"/>
+      <c r="M18" s="46" t="inlineStr"/>
+      <c r="N18" s="46" t="inlineStr"/>
+      <c r="O18" s="46" t="inlineStr"/>
+      <c r="P18" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q18" s="46" t="inlineStr"/>
+      <c r="R18" s="46" t="inlineStr"/>
+      <c r="S18" s="46" t="inlineStr"/>
+      <c r="T18" s="46" t="inlineStr"/>
+      <c r="U18" s="46" t="inlineStr"/>
+      <c r="V18" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="W18" s="46" t="inlineStr"/>
+      <c r="X18" s="46" t="inlineStr"/>
+      <c r="Y18" s="46" t="inlineStr"/>
+      <c r="Z18" s="46" t="inlineStr"/>
+      <c r="AA18" s="45" t="n">
+        <v>757</v>
+      </c>
+      <c r="AB18" s="46" t="inlineStr"/>
+      <c r="AC18" s="46" t="inlineStr"/>
+      <c r="AD18" s="46" t="inlineStr"/>
+      <c r="AE18" s="46" t="inlineStr"/>
+      <c r="AF18" s="46" t="inlineStr"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Inventory levels (end of period)</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="n"/>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="42" t="n"/>
+      <c r="I20" s="42" t="n"/>
+      <c r="J20" s="42" t="n"/>
+      <c r="K20" s="42" t="n"/>
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="42" t="n"/>
+      <c r="N20" s="42" t="n"/>
+      <c r="O20" s="42" t="n"/>
+      <c r="P20" s="42" t="n"/>
+      <c r="Q20" s="42" t="n"/>
+      <c r="R20" s="42" t="n"/>
+      <c r="S20" s="42" t="n"/>
+      <c r="T20" s="42" t="n"/>
+      <c r="U20" s="42" t="n"/>
+      <c r="V20" s="42" t="n"/>
+      <c r="W20" s="42" t="n"/>
+      <c r="X20" s="42" t="n"/>
+      <c r="Y20" s="42" t="n"/>
+      <c r="Z20" s="42" t="n"/>
+      <c r="AA20" s="42" t="n"/>
+      <c r="AB20" s="42" t="n"/>
+      <c r="AC20" s="42" t="n"/>
+      <c r="AD20" s="42" t="n"/>
+      <c r="AE20" s="42" t="n"/>
+      <c r="AF20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H21" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I21" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K21" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L21" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M21" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N21" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O21" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P21" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q21" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R21" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S21" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T21" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U21" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V21" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W21" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X21" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y21" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z21" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA21" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB21" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC21" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD21" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE21" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF21" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>B1401</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="n">
+        <v>6400</v>
+      </c>
+      <c r="D22" s="47" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E22" s="47" t="n">
+        <v>6400</v>
+      </c>
+      <c r="F22" s="47" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G22" s="47" t="n">
+        <v>9716</v>
+      </c>
+      <c r="H22" s="47" t="n">
+        <v>1049</v>
+      </c>
+      <c r="I22" s="47" t="n">
+        <v>4382</v>
+      </c>
+      <c r="J22" s="47" t="n">
+        <v>4382</v>
+      </c>
+      <c r="K22" s="47" t="n">
+        <v>7715</v>
+      </c>
+      <c r="L22" s="47" t="n">
+        <v>11048</v>
+      </c>
+      <c r="M22" s="47" t="n">
+        <v>1581</v>
+      </c>
+      <c r="N22" s="47" t="n">
+        <v>1581</v>
+      </c>
+      <c r="O22" s="47" t="n">
+        <v>1581</v>
+      </c>
+      <c r="P22" s="47" t="n">
+        <v>4914</v>
+      </c>
+      <c r="Q22" s="47" t="n">
+        <v>8247</v>
+      </c>
+      <c r="R22" s="47" t="n">
+        <v>11580</v>
+      </c>
+      <c r="S22" s="47" t="n">
+        <v>2113</v>
+      </c>
+      <c r="T22" s="47" t="n">
+        <v>2113</v>
+      </c>
+      <c r="U22" s="47" t="n">
+        <v>2113</v>
+      </c>
+      <c r="V22" s="47" t="n">
+        <v>5446</v>
+      </c>
+      <c r="W22" s="47" t="n">
+        <v>8779</v>
+      </c>
+      <c r="X22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>B2302</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D23" s="47" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E23" s="47" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F23" s="47" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G23" s="47" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="47" t="n">
+        <v>4600</v>
+      </c>
+      <c r="M23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="47" t="n">
+        <v>4600</v>
+      </c>
+      <c r="S23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="47" t="n">
+        <v>4084</v>
+      </c>
+      <c r="X23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>B3201</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D24" s="47" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E24" s="47" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F24" s="47" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G24" s="47" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H24" s="47" t="n">
+        <v>400</v>
+      </c>
+      <c r="I24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>B4702</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D25" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E25" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F25" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G25" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>V1501</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D26" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E26" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G26" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H26" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I26" s="47" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>V6302</t>
+        </is>
+      </c>
+      <c r="C27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="n">
+        <v>1214</v>
+      </c>
+      <c r="D28" s="47" t="n">
+        <v>1720</v>
+      </c>
+      <c r="E28" s="47" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F28" s="47" t="n">
+        <v>1334</v>
+      </c>
+      <c r="G28" s="47" t="n">
+        <v>1163</v>
+      </c>
+      <c r="H28" s="47" t="n">
+        <v>968</v>
+      </c>
+      <c r="I28" s="47" t="n">
+        <v>554</v>
+      </c>
+      <c r="J28" s="47" t="n">
+        <v>407</v>
+      </c>
+      <c r="K28" s="47" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L28" s="47" t="n">
+        <v>1583</v>
+      </c>
+      <c r="M28" s="47" t="n">
+        <v>1375</v>
+      </c>
+      <c r="N28" s="47" t="n">
+        <v>1197</v>
+      </c>
+      <c r="O28" s="47" t="n">
+        <v>1029</v>
+      </c>
+      <c r="P28" s="47" t="n">
+        <v>821</v>
+      </c>
+      <c r="Q28" s="47" t="n">
+        <v>1448</v>
+      </c>
+      <c r="R28" s="47" t="n">
+        <v>1280</v>
+      </c>
+      <c r="S28" s="47" t="n">
+        <v>1099</v>
+      </c>
+      <c r="T28" s="47" t="n">
+        <v>911</v>
+      </c>
+      <c r="U28" s="47" t="n">
+        <v>699</v>
+      </c>
+      <c r="V28" s="47" t="n">
+        <v>446</v>
+      </c>
+      <c r="W28" s="47" t="n">
+        <v>1027</v>
+      </c>
+      <c r="X28" s="47" t="n">
+        <v>831</v>
+      </c>
+      <c r="Y28" s="47" t="n">
+        <v>605</v>
+      </c>
+      <c r="Z28" s="47" t="n">
+        <v>366</v>
+      </c>
+      <c r="AA28" s="47" t="n">
+        <v>146</v>
+      </c>
+      <c r="AB28" s="47" t="n">
+        <v>704</v>
+      </c>
+      <c r="AC28" s="47" t="n">
+        <v>521</v>
+      </c>
+      <c r="AD28" s="47" t="n">
+        <v>372</v>
+      </c>
+      <c r="AE28" s="47" t="n">
+        <v>205</v>
+      </c>
+      <c r="AF28" s="48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>Capacity usage per week</t>
+        </is>
+      </c>
+      <c r="C30" s="42" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="42" t="n"/>
+      <c r="H30" s="42" t="n"/>
+      <c r="I30" s="42" t="n"/>
+      <c r="J30" s="42" t="n"/>
+      <c r="K30" s="42" t="n"/>
+      <c r="L30" s="42" t="n"/>
+      <c r="M30" s="42" t="n"/>
+      <c r="N30" s="42" t="n"/>
+      <c r="O30" s="42" t="n"/>
+      <c r="P30" s="42" t="n"/>
+      <c r="Q30" s="42" t="n"/>
+      <c r="R30" s="42" t="n"/>
+      <c r="S30" s="42" t="n"/>
+      <c r="T30" s="42" t="n"/>
+      <c r="U30" s="42" t="n"/>
+      <c r="V30" s="42" t="n"/>
+      <c r="W30" s="42" t="n"/>
+      <c r="X30" s="42" t="n"/>
+      <c r="Y30" s="42" t="n"/>
+      <c r="Z30" s="42" t="n"/>
+      <c r="AA30" s="42" t="n"/>
+      <c r="AB30" s="42" t="n"/>
+      <c r="AC30" s="42" t="n"/>
+      <c r="AD30" s="42" t="n"/>
+      <c r="AE30" s="42" t="n"/>
+      <c r="AF30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="43" t="inlineStr"/>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G31" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H31" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I31" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K31" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L31" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M31" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N31" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O31" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P31" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q31" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R31" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S31" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T31" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U31" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V31" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W31" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X31" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y31" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z31" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA31" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB31" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC31" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD31" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE31" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF31" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>X  (units)</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="n">
+        <v>650</v>
+      </c>
+      <c r="D32" s="56" t="inlineStr"/>
+      <c r="E32" s="56" t="inlineStr"/>
+      <c r="F32" s="56" t="inlineStr"/>
+      <c r="G32" s="56" t="inlineStr"/>
+      <c r="H32" s="56" t="inlineStr"/>
+      <c r="I32" s="56" t="inlineStr"/>
+      <c r="J32" s="55" t="n">
+        <v>800</v>
+      </c>
+      <c r="K32" s="47" t="n">
+        <v>750</v>
+      </c>
+      <c r="L32" s="56" t="inlineStr"/>
+      <c r="M32" s="56" t="inlineStr"/>
+      <c r="N32" s="56" t="inlineStr"/>
+      <c r="O32" s="56" t="inlineStr"/>
+      <c r="P32" s="55" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q32" s="56" t="inlineStr"/>
+      <c r="R32" s="56" t="inlineStr"/>
+      <c r="S32" s="56" t="inlineStr"/>
+      <c r="T32" s="56" t="inlineStr"/>
+      <c r="U32" s="56" t="inlineStr"/>
+      <c r="V32" s="55" t="n">
+        <v>800</v>
+      </c>
+      <c r="W32" s="56" t="inlineStr"/>
+      <c r="X32" s="56" t="inlineStr"/>
+      <c r="Y32" s="56" t="inlineStr"/>
+      <c r="Z32" s="56" t="inlineStr"/>
+      <c r="AA32" s="47" t="n">
+        <v>757</v>
+      </c>
+      <c r="AB32" s="56" t="inlineStr"/>
+      <c r="AC32" s="56" t="inlineStr"/>
+      <c r="AD32" s="56" t="inlineStr"/>
+      <c r="AE32" s="56" t="inlineStr"/>
+      <c r="AF32" s="56" t="inlineStr"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>Y  (min)</t>
+        </is>
+      </c>
+      <c r="C33" s="55" t="n">
+        <v>9948</v>
+      </c>
+      <c r="D33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="F33" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="I33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="J33" s="47" t="n">
+        <v>9200</v>
+      </c>
+      <c r="K33" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="N33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="O33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="P33" s="47" t="n">
+        <v>9200</v>
+      </c>
+      <c r="Q33" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="S33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="T33" s="55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="U33" s="47" t="n">
+        <v>8168</v>
+      </c>
+      <c r="V33" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W33" s="56" t="inlineStr"/>
+      <c r="X33" s="56" t="inlineStr"/>
+      <c r="Y33" s="56" t="inlineStr"/>
+      <c r="Z33" s="56" t="inlineStr"/>
+      <c r="AA33" s="56" t="inlineStr"/>
+      <c r="AB33" s="56" t="inlineStr"/>
+      <c r="AC33" s="56" t="inlineStr"/>
+      <c r="AD33" s="56" t="inlineStr"/>
+      <c r="AE33" s="56" t="inlineStr"/>
+      <c r="AF33" s="56" t="inlineStr"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>X  (% used)</t>
+        </is>
+      </c>
+      <c r="C34" s="57" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="D34" s="56" t="inlineStr"/>
+      <c r="E34" s="56" t="inlineStr"/>
+      <c r="F34" s="56" t="inlineStr"/>
+      <c r="G34" s="56" t="inlineStr"/>
+      <c r="H34" s="56" t="inlineStr"/>
+      <c r="I34" s="56" t="inlineStr"/>
+      <c r="J34" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="57" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="L34" s="56" t="inlineStr"/>
+      <c r="M34" s="56" t="inlineStr"/>
+      <c r="N34" s="56" t="inlineStr"/>
+      <c r="O34" s="56" t="inlineStr"/>
+      <c r="P34" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="56" t="inlineStr"/>
+      <c r="R34" s="56" t="inlineStr"/>
+      <c r="S34" s="56" t="inlineStr"/>
+      <c r="T34" s="56" t="inlineStr"/>
+      <c r="U34" s="56" t="inlineStr"/>
+      <c r="V34" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" s="56" t="inlineStr"/>
+      <c r="X34" s="56" t="inlineStr"/>
+      <c r="Y34" s="56" t="inlineStr"/>
+      <c r="Z34" s="56" t="inlineStr"/>
+      <c r="AA34" s="57" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="AB34" s="56" t="inlineStr"/>
+      <c r="AC34" s="56" t="inlineStr"/>
+      <c r="AD34" s="56" t="inlineStr"/>
+      <c r="AE34" s="56" t="inlineStr"/>
+      <c r="AF34" s="56" t="inlineStr"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>Y  (% used)</t>
+        </is>
+      </c>
+      <c r="C35" s="58" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="57" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="57" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Q35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" s="57" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="V35" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="56" t="inlineStr"/>
+      <c r="X35" s="56" t="inlineStr"/>
+      <c r="Y35" s="56" t="inlineStr"/>
+      <c r="Z35" s="56" t="inlineStr"/>
+      <c r="AA35" s="56" t="inlineStr"/>
+      <c r="AB35" s="56" t="inlineStr"/>
+      <c r="AC35" s="56" t="inlineStr"/>
+      <c r="AD35" s="56" t="inlineStr"/>
+      <c r="AE35" s="56" t="inlineStr"/>
+      <c r="AF35" s="56" t="inlineStr"/>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Setup decisions</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="n"/>
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="42" t="n"/>
+      <c r="G37" s="42" t="n"/>
+      <c r="H37" s="42" t="n"/>
+      <c r="I37" s="42" t="n"/>
+      <c r="J37" s="42" t="n"/>
+      <c r="K37" s="42" t="n"/>
+      <c r="L37" s="42" t="n"/>
+      <c r="M37" s="42" t="n"/>
+      <c r="N37" s="42" t="n"/>
+      <c r="O37" s="42" t="n"/>
+      <c r="P37" s="42" t="n"/>
+      <c r="Q37" s="42" t="n"/>
+      <c r="R37" s="42" t="n"/>
+      <c r="S37" s="42" t="n"/>
+      <c r="T37" s="42" t="n"/>
+      <c r="U37" s="42" t="n"/>
+      <c r="V37" s="42" t="n"/>
+      <c r="W37" s="42" t="n"/>
+      <c r="X37" s="42" t="n"/>
+      <c r="Y37" s="42" t="n"/>
+      <c r="Z37" s="42" t="n"/>
+      <c r="AA37" s="42" t="n"/>
+      <c r="AB37" s="42" t="n"/>
+      <c r="AC37" s="42" t="n"/>
+      <c r="AD37" s="42" t="n"/>
+      <c r="AE37" s="42" t="n"/>
+      <c r="AF37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F38" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H38" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I38" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J38" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K38" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L38" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M38" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N38" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O38" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P38" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q38" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R38" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S38" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T38" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U38" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V38" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W38" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X38" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y38" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z38" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA38" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB38" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC38" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD38" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE38" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF38" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>B1401</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="inlineStr"/>
+      <c r="G39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J39" s="49" t="inlineStr"/>
+      <c r="K39" s="49" t="inlineStr"/>
+      <c r="L39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P39" s="49" t="inlineStr"/>
+      <c r="Q39" s="49" t="inlineStr"/>
+      <c r="R39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T39" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U39" s="49" t="inlineStr"/>
+      <c r="V39" s="49" t="inlineStr"/>
+      <c r="W39" s="49" t="inlineStr"/>
+      <c r="X39" s="49" t="inlineStr"/>
+      <c r="Y39" s="49" t="inlineStr"/>
+      <c r="Z39" s="49" t="inlineStr"/>
+      <c r="AA39" s="49" t="inlineStr"/>
+      <c r="AB39" s="49" t="inlineStr"/>
+      <c r="AC39" s="49" t="inlineStr"/>
+      <c r="AD39" s="49" t="inlineStr"/>
+      <c r="AE39" s="49" t="inlineStr"/>
+      <c r="AF39" s="49" t="inlineStr"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>B2302</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="inlineStr"/>
+      <c r="D40" s="49" t="inlineStr"/>
+      <c r="E40" s="49" t="inlineStr"/>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G40" s="49" t="inlineStr"/>
+      <c r="H40" s="49" t="inlineStr"/>
+      <c r="I40" s="49" t="inlineStr"/>
+      <c r="J40" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K40" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L40" s="49" t="inlineStr"/>
+      <c r="M40" s="49" t="inlineStr"/>
+      <c r="N40" s="49" t="inlineStr"/>
+      <c r="O40" s="49" t="inlineStr"/>
+      <c r="P40" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q40" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R40" s="49" t="inlineStr"/>
+      <c r="S40" s="49" t="inlineStr"/>
+      <c r="T40" s="49" t="inlineStr"/>
+      <c r="U40" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V40" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W40" s="49" t="inlineStr"/>
+      <c r="X40" s="49" t="inlineStr"/>
+      <c r="Y40" s="49" t="inlineStr"/>
+      <c r="Z40" s="49" t="inlineStr"/>
+      <c r="AA40" s="49" t="inlineStr"/>
+      <c r="AB40" s="49" t="inlineStr"/>
+      <c r="AC40" s="49" t="inlineStr"/>
+      <c r="AD40" s="49" t="inlineStr"/>
+      <c r="AE40" s="49" t="inlineStr"/>
+      <c r="AF40" s="49" t="inlineStr"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>B3201</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr"/>
+      <c r="D41" s="49" t="inlineStr"/>
+      <c r="E41" s="49" t="inlineStr"/>
+      <c r="F41" s="49" t="inlineStr"/>
+      <c r="G41" s="49" t="inlineStr"/>
+      <c r="H41" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I41" s="49" t="inlineStr"/>
+      <c r="J41" s="49" t="inlineStr"/>
+      <c r="K41" s="49" t="inlineStr"/>
+      <c r="L41" s="49" t="inlineStr"/>
+      <c r="M41" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N41" s="49" t="inlineStr"/>
+      <c r="O41" s="49" t="inlineStr"/>
+      <c r="P41" s="49" t="inlineStr"/>
+      <c r="Q41" s="49" t="inlineStr"/>
+      <c r="R41" s="49" t="inlineStr"/>
+      <c r="S41" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T41" s="49" t="inlineStr"/>
+      <c r="U41" s="49" t="inlineStr"/>
+      <c r="V41" s="49" t="inlineStr"/>
+      <c r="W41" s="49" t="inlineStr"/>
+      <c r="X41" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y41" s="49" t="inlineStr"/>
+      <c r="Z41" s="49" t="inlineStr"/>
+      <c r="AA41" s="49" t="inlineStr"/>
+      <c r="AB41" s="49" t="inlineStr"/>
+      <c r="AC41" s="49" t="inlineStr"/>
+      <c r="AD41" s="49" t="inlineStr"/>
+      <c r="AE41" s="49" t="inlineStr"/>
+      <c r="AF41" s="49" t="inlineStr"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>B4702</t>
+        </is>
+      </c>
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr"/>
+      <c r="F42" s="49" t="inlineStr"/>
+      <c r="G42" s="49" t="inlineStr"/>
+      <c r="H42" s="49" t="inlineStr"/>
+      <c r="I42" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J42" s="49" t="inlineStr"/>
+      <c r="K42" s="49" t="inlineStr"/>
+      <c r="L42" s="49" t="inlineStr"/>
+      <c r="M42" s="49" t="inlineStr"/>
+      <c r="N42" s="49" t="inlineStr"/>
+      <c r="O42" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P42" s="49" t="inlineStr"/>
+      <c r="Q42" s="49" t="inlineStr"/>
+      <c r="R42" s="49" t="inlineStr"/>
+      <c r="S42" s="49" t="inlineStr"/>
+      <c r="T42" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U42" s="49" t="inlineStr"/>
+      <c r="V42" s="49" t="inlineStr"/>
+      <c r="W42" s="49" t="inlineStr"/>
+      <c r="X42" s="49" t="inlineStr"/>
+      <c r="Y42" s="49" t="inlineStr"/>
+      <c r="Z42" s="49" t="inlineStr"/>
+      <c r="AA42" s="49" t="inlineStr"/>
+      <c r="AB42" s="49" t="inlineStr"/>
+      <c r="AC42" s="49" t="inlineStr"/>
+      <c r="AD42" s="49" t="inlineStr"/>
+      <c r="AE42" s="49" t="inlineStr"/>
+      <c r="AF42" s="49" t="inlineStr"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>V1501</t>
+        </is>
+      </c>
+      <c r="C43" s="49" t="inlineStr"/>
+      <c r="D43" s="49" t="inlineStr"/>
+      <c r="E43" s="49" t="inlineStr"/>
+      <c r="F43" s="49" t="inlineStr"/>
+      <c r="G43" s="49" t="inlineStr"/>
+      <c r="H43" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I43" s="49" t="inlineStr"/>
+      <c r="J43" s="49" t="inlineStr"/>
+      <c r="K43" s="49" t="inlineStr"/>
+      <c r="L43" s="49" t="inlineStr"/>
+      <c r="M43" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N43" s="49" t="inlineStr"/>
+      <c r="O43" s="49" t="inlineStr"/>
+      <c r="P43" s="49" t="inlineStr"/>
+      <c r="Q43" s="49" t="inlineStr"/>
+      <c r="R43" s="49" t="inlineStr"/>
+      <c r="S43" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T43" s="49" t="inlineStr"/>
+      <c r="U43" s="49" t="inlineStr"/>
+      <c r="V43" s="49" t="inlineStr"/>
+      <c r="W43" s="49" t="inlineStr"/>
+      <c r="X43" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y43" s="49" t="inlineStr"/>
+      <c r="Z43" s="49" t="inlineStr"/>
+      <c r="AA43" s="49" t="inlineStr"/>
+      <c r="AB43" s="49" t="inlineStr"/>
+      <c r="AC43" s="49" t="inlineStr"/>
+      <c r="AD43" s="49" t="inlineStr"/>
+      <c r="AE43" s="49" t="inlineStr"/>
+      <c r="AF43" s="49" t="inlineStr"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>V6302</t>
+        </is>
+      </c>
+      <c r="C44" s="49" t="inlineStr"/>
+      <c r="D44" s="49" t="inlineStr"/>
+      <c r="E44" s="49" t="inlineStr"/>
+      <c r="F44" s="49" t="inlineStr"/>
+      <c r="G44" s="49" t="inlineStr"/>
+      <c r="H44" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I44" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J44" s="49" t="inlineStr"/>
+      <c r="K44" s="49" t="inlineStr"/>
+      <c r="L44" s="49" t="inlineStr"/>
+      <c r="M44" s="49" t="inlineStr"/>
+      <c r="N44" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O44" s="49" t="inlineStr"/>
+      <c r="P44" s="49" t="inlineStr"/>
+      <c r="Q44" s="49" t="inlineStr"/>
+      <c r="R44" s="49" t="inlineStr"/>
+      <c r="S44" s="49" t="inlineStr"/>
+      <c r="T44" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U44" s="49" t="inlineStr"/>
+      <c r="V44" s="49" t="inlineStr"/>
+      <c r="W44" s="49" t="inlineStr"/>
+      <c r="X44" s="49" t="inlineStr"/>
+      <c r="Y44" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z44" s="49" t="inlineStr"/>
+      <c r="AA44" s="49" t="inlineStr"/>
+      <c r="AB44" s="49" t="inlineStr"/>
+      <c r="AC44" s="49" t="inlineStr"/>
+      <c r="AD44" s="49" t="inlineStr"/>
+      <c r="AE44" s="49" t="inlineStr"/>
+      <c r="AF44" s="49" t="inlineStr"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
+      </c>
+      <c r="C45" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr"/>
+      <c r="E45" s="49" t="inlineStr"/>
+      <c r="F45" s="49" t="inlineStr"/>
+      <c r="G45" s="49" t="inlineStr"/>
+      <c r="H45" s="49" t="inlineStr"/>
+      <c r="I45" s="49" t="inlineStr"/>
+      <c r="J45" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K45" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L45" s="49" t="inlineStr"/>
+      <c r="M45" s="49" t="inlineStr"/>
+      <c r="N45" s="49" t="inlineStr"/>
+      <c r="O45" s="49" t="inlineStr"/>
+      <c r="P45" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q45" s="49" t="inlineStr"/>
+      <c r="R45" s="49" t="inlineStr"/>
+      <c r="S45" s="49" t="inlineStr"/>
+      <c r="T45" s="49" t="inlineStr"/>
+      <c r="U45" s="49" t="inlineStr"/>
+      <c r="V45" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W45" s="49" t="inlineStr"/>
+      <c r="X45" s="49" t="inlineStr"/>
+      <c r="Y45" s="49" t="inlineStr"/>
+      <c r="Z45" s="49" t="inlineStr"/>
+      <c r="AA45" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB45" s="49" t="inlineStr"/>
+      <c r="AC45" s="49" t="inlineStr"/>
+      <c r="AD45" s="49" t="inlineStr"/>
+      <c r="AE45" s="49" t="inlineStr"/>
+      <c r="AF45" s="49" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C3:AF3"/>
+    <mergeCell ref="C8:AF8"/>
+    <mergeCell ref="C4:AF4"/>
+    <mergeCell ref="C7:AF7"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="C5:AF5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:AF59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="5.5" customWidth="1" min="6" max="6"/>
+    <col width="5.5" customWidth="1" min="7" max="7"/>
+    <col width="5.5" customWidth="1" min="8" max="8"/>
+    <col width="5.5" customWidth="1" min="9" max="9"/>
+    <col width="5.5" customWidth="1" min="10" max="10"/>
+    <col width="5.5" customWidth="1" min="11" max="11"/>
+    <col width="5.5" customWidth="1" min="12" max="12"/>
+    <col width="5.5" customWidth="1" min="13" max="13"/>
+    <col width="5.5" customWidth="1" min="14" max="14"/>
+    <col width="5.5" customWidth="1" min="15" max="15"/>
+    <col width="5.5" customWidth="1" min="16" max="16"/>
+    <col width="5.5" customWidth="1" min="17" max="17"/>
+    <col width="5.5" customWidth="1" min="18" max="18"/>
+    <col width="5.5" customWidth="1" min="19" max="19"/>
+    <col width="5.5" customWidth="1" min="20" max="20"/>
+    <col width="5.5" customWidth="1" min="21" max="21"/>
+    <col width="5.5" customWidth="1" min="22" max="22"/>
+    <col width="5.5" customWidth="1" min="23" max="23"/>
+    <col width="5.5" customWidth="1" min="24" max="24"/>
+    <col width="5.5" customWidth="1" min="25" max="25"/>
+    <col width="5.5" customWidth="1" min="26" max="26"/>
+    <col width="5.5" customWidth="1" min="27" max="27"/>
+    <col width="5.5" customWidth="1" min="28" max="28"/>
+    <col width="5.5" customWidth="1" min="29" max="29"/>
+    <col width="5.5" customWidth="1" min="30" max="30"/>
+    <col width="5.5" customWidth="1" min="31" max="31"/>
+    <col width="5.5" customWidth="1" min="32" max="32"/>
+    <col width="5.5" customWidth="1" min="33" max="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="37" t="inlineStr">
+        <is>
+          <t>Assignment 2b - Realized demand evaluation (finite capacity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1"/>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>Setup cost</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="n">
+        <v>145500</v>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>Holding cost</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="n">
+        <v>401114.8</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>Backorder cost</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="n">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>Total cost</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="n">
+        <v>574114.8</v>
+      </c>
+    </row>
+    <row r="7" ht="6" customHeight="1"/>
+    <row r="8" ht="14" customHeight="1">
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>Service metrics (end product)</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="42" t="n"/>
+      <c r="E8" s="42" t="n"/>
+      <c r="F8" s="42" t="n"/>
+      <c r="G8" s="42" t="n"/>
+      <c r="H8" s="42" t="n"/>
+      <c r="I8" s="42" t="n"/>
+      <c r="J8" s="42" t="n"/>
+      <c r="K8" s="42" t="n"/>
+      <c r="L8" s="42" t="n"/>
+      <c r="M8" s="42" t="n"/>
+      <c r="N8" s="42" t="n"/>
+      <c r="O8" s="42" t="n"/>
+      <c r="P8" s="42" t="n"/>
+      <c r="Q8" s="42" t="n"/>
+      <c r="R8" s="42" t="n"/>
+      <c r="S8" s="42" t="n"/>
+      <c r="T8" s="42" t="n"/>
+      <c r="U8" s="42" t="n"/>
+      <c r="V8" s="42" t="n"/>
+      <c r="W8" s="42" t="n"/>
+      <c r="X8" s="42" t="n"/>
+      <c r="Y8" s="42" t="n"/>
+      <c r="Z8" s="42" t="n"/>
+      <c r="AA8" s="42" t="n"/>
+      <c r="AB8" s="42" t="n"/>
+      <c r="AC8" s="42" t="n"/>
+      <c r="AD8" s="42" t="n"/>
+      <c r="AE8" s="42" t="n"/>
+      <c r="AF8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>Service level</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>96.7%  (29/30 periods fully met)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>Fill rate</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>98.17%  (5,907 / 6,017 units delivered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Total backordered</t>
+        </is>
+      </c>
+      <c r="C11" s="59" t="inlineStr">
+        <is>
+          <t>110 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Comparison: 1b (infinite capacity) vs 2b (finite capacity)</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="42" t="n"/>
+      <c r="J13" s="42" t="n"/>
+      <c r="K13" s="42" t="n"/>
+      <c r="L13" s="42" t="n"/>
+      <c r="M13" s="42" t="n"/>
+      <c r="N13" s="42" t="n"/>
+      <c r="O13" s="42" t="n"/>
+      <c r="P13" s="42" t="n"/>
+      <c r="Q13" s="42" t="n"/>
+      <c r="R13" s="42" t="n"/>
+      <c r="S13" s="42" t="n"/>
+      <c r="T13" s="42" t="n"/>
+      <c r="U13" s="42" t="n"/>
+      <c r="V13" s="42" t="n"/>
+      <c r="W13" s="42" t="n"/>
+      <c r="X13" s="42" t="n"/>
+      <c r="Y13" s="42" t="n"/>
+      <c r="Z13" s="42" t="n"/>
+      <c r="AA13" s="42" t="n"/>
+      <c r="AB13" s="42" t="n"/>
+      <c r="AC13" s="42" t="n"/>
+      <c r="AD13" s="42" t="n"/>
+      <c r="AE13" s="42" t="n"/>
+      <c r="AF13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>Total cost (EUR)</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="n">
+        <v>447792</v>
+      </c>
+      <c r="D15" s="60" t="n">
+        <v>574114.8</v>
+      </c>
+      <c r="E15" s="61" t="n">
+        <v>126322.8</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>Setup cost (EUR)</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="n">
+        <v>79500</v>
+      </c>
+      <c r="D16" s="60" t="n">
+        <v>145500</v>
+      </c>
+      <c r="E16" s="61" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>Holding cost (EUR)</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="n">
+        <v>321542</v>
+      </c>
+      <c r="D17" s="60" t="n">
+        <v>401114.8</v>
+      </c>
+      <c r="E17" s="61" t="n">
+        <v>79572.8</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Backorder cost (EUR)</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="n">
+        <v>46750</v>
+      </c>
+      <c r="D18" s="60" t="n">
+        <v>27500</v>
+      </c>
+      <c r="E18" s="62" t="n">
+        <v>-19250</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>Service level (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="D19" s="63" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="E19" s="64" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>Fill rate (%)</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="D20" s="65" t="n">
+        <v>98.17</v>
+      </c>
+      <c r="E20" s="66" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>Production / order schedule (units)</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n"/>
+      <c r="I22" s="42" t="n"/>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="42" t="n"/>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="42" t="n"/>
+      <c r="N22" s="42" t="n"/>
+      <c r="O22" s="42" t="n"/>
+      <c r="P22" s="42" t="n"/>
+      <c r="Q22" s="42" t="n"/>
+      <c r="R22" s="42" t="n"/>
+      <c r="S22" s="42" t="n"/>
+      <c r="T22" s="42" t="n"/>
+      <c r="U22" s="42" t="n"/>
+      <c r="V22" s="42" t="n"/>
+      <c r="W22" s="42" t="n"/>
+      <c r="X22" s="42" t="n"/>
+      <c r="Y22" s="42" t="n"/>
+      <c r="Z22" s="42" t="n"/>
+      <c r="AA22" s="42" t="n"/>
+      <c r="AB22" s="42" t="n"/>
+      <c r="AC22" s="42" t="n"/>
+      <c r="AD22" s="42" t="n"/>
+      <c r="AE22" s="42" t="n"/>
+      <c r="AF22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G23" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H23" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I23" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K23" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L23" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M23" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N23" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O23" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P23" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q23" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R23" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S23" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T23" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U23" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V23" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W23" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X23" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y23" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z23" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA23" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB23" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC23" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD23" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE23" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF23" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>B1401</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="n">
+        <v>3316</v>
+      </c>
+      <c r="D24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="E24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="F24" s="46" t="inlineStr"/>
+      <c r="G24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="H24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="I24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="J24" s="46" t="inlineStr"/>
+      <c r="K24" s="46" t="inlineStr"/>
+      <c r="L24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="M24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="N24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="O24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="P24" s="46" t="inlineStr"/>
+      <c r="Q24" s="46" t="inlineStr"/>
+      <c r="R24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="S24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="T24" s="45" t="n">
+        <v>3333</v>
+      </c>
+      <c r="U24" s="46" t="inlineStr"/>
+      <c r="V24" s="46" t="inlineStr"/>
+      <c r="W24" s="46" t="inlineStr"/>
+      <c r="X24" s="46" t="inlineStr"/>
+      <c r="Y24" s="46" t="inlineStr"/>
+      <c r="Z24" s="46" t="inlineStr"/>
+      <c r="AA24" s="46" t="inlineStr"/>
+      <c r="AB24" s="46" t="inlineStr"/>
+      <c r="AC24" s="46" t="inlineStr"/>
+      <c r="AD24" s="46" t="inlineStr"/>
+      <c r="AE24" s="46" t="inlineStr"/>
+      <c r="AF24" s="46" t="inlineStr"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>B2302</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr"/>
+      <c r="D25" s="46" t="inlineStr"/>
+      <c r="E25" s="46" t="inlineStr"/>
+      <c r="F25" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G25" s="46" t="inlineStr"/>
+      <c r="H25" s="46" t="inlineStr"/>
+      <c r="I25" s="46" t="inlineStr"/>
+      <c r="J25" s="45" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K25" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L25" s="46" t="inlineStr"/>
+      <c r="M25" s="46" t="inlineStr"/>
+      <c r="N25" s="46" t="inlineStr"/>
+      <c r="O25" s="46" t="inlineStr"/>
+      <c r="P25" s="45" t="n">
+        <v>4600</v>
+      </c>
+      <c r="Q25" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R25" s="46" t="inlineStr"/>
+      <c r="S25" s="46" t="inlineStr"/>
+      <c r="T25" s="46" t="inlineStr"/>
+      <c r="U25" s="45" t="n">
+        <v>4084</v>
+      </c>
+      <c r="V25" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W25" s="46" t="inlineStr"/>
+      <c r="X25" s="46" t="inlineStr"/>
+      <c r="Y25" s="46" t="inlineStr"/>
+      <c r="Z25" s="46" t="inlineStr"/>
+      <c r="AA25" s="46" t="inlineStr"/>
+      <c r="AB25" s="46" t="inlineStr"/>
+      <c r="AC25" s="46" t="inlineStr"/>
+      <c r="AD25" s="46" t="inlineStr"/>
+      <c r="AE25" s="46" t="inlineStr"/>
+      <c r="AF25" s="46" t="inlineStr"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>B3201</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr"/>
+      <c r="D26" s="46" t="inlineStr"/>
+      <c r="E26" s="46" t="inlineStr"/>
+      <c r="F26" s="46" t="inlineStr"/>
+      <c r="G26" s="46" t="inlineStr"/>
+      <c r="H26" s="45" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I26" s="46" t="inlineStr"/>
+      <c r="J26" s="46" t="inlineStr"/>
+      <c r="K26" s="46" t="inlineStr"/>
+      <c r="L26" s="46" t="inlineStr"/>
+      <c r="M26" s="45" t="n">
+        <v>4800</v>
+      </c>
+      <c r="N26" s="46" t="inlineStr"/>
+      <c r="O26" s="46" t="inlineStr"/>
+      <c r="P26" s="46" t="inlineStr"/>
+      <c r="Q26" s="46" t="inlineStr"/>
+      <c r="R26" s="46" t="inlineStr"/>
+      <c r="S26" s="45" t="n">
+        <v>4800</v>
+      </c>
+      <c r="T26" s="46" t="inlineStr"/>
+      <c r="U26" s="46" t="inlineStr"/>
+      <c r="V26" s="46" t="inlineStr"/>
+      <c r="W26" s="46" t="inlineStr"/>
+      <c r="X26" s="45" t="n">
+        <v>4542</v>
+      </c>
+      <c r="Y26" s="46" t="inlineStr"/>
+      <c r="Z26" s="46" t="inlineStr"/>
+      <c r="AA26" s="46" t="inlineStr"/>
+      <c r="AB26" s="46" t="inlineStr"/>
+      <c r="AC26" s="46" t="inlineStr"/>
+      <c r="AD26" s="46" t="inlineStr"/>
+      <c r="AE26" s="46" t="inlineStr"/>
+      <c r="AF26" s="46" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>B4702</t>
+        </is>
+      </c>
+      <c r="C27" s="45" t="n">
+        <v>13600</v>
+      </c>
+      <c r="D27" s="45" t="n">
+        <v>15750</v>
+      </c>
+      <c r="E27" s="46" t="inlineStr"/>
+      <c r="F27" s="46" t="inlineStr"/>
+      <c r="G27" s="46" t="inlineStr"/>
+      <c r="H27" s="46" t="inlineStr"/>
+      <c r="I27" s="45" t="n">
+        <v>16800</v>
+      </c>
+      <c r="J27" s="46" t="inlineStr"/>
+      <c r="K27" s="46" t="inlineStr"/>
+      <c r="L27" s="46" t="inlineStr"/>
+      <c r="M27" s="46" t="inlineStr"/>
+      <c r="N27" s="46" t="inlineStr"/>
+      <c r="O27" s="45" t="n">
+        <v>16800</v>
+      </c>
+      <c r="P27" s="46" t="inlineStr"/>
+      <c r="Q27" s="46" t="inlineStr"/>
+      <c r="R27" s="46" t="inlineStr"/>
+      <c r="S27" s="46" t="inlineStr"/>
+      <c r="T27" s="45" t="n">
+        <v>15897</v>
+      </c>
+      <c r="U27" s="46" t="inlineStr"/>
+      <c r="V27" s="46" t="inlineStr"/>
+      <c r="W27" s="46" t="inlineStr"/>
+      <c r="X27" s="46" t="inlineStr"/>
+      <c r="Y27" s="46" t="inlineStr"/>
+      <c r="Z27" s="46" t="inlineStr"/>
+      <c r="AA27" s="46" t="inlineStr"/>
+      <c r="AB27" s="46" t="inlineStr"/>
+      <c r="AC27" s="46" t="inlineStr"/>
+      <c r="AD27" s="46" t="inlineStr"/>
+      <c r="AE27" s="46" t="inlineStr"/>
+      <c r="AF27" s="46" t="inlineStr"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>V1501</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr"/>
+      <c r="D28" s="46" t="inlineStr"/>
+      <c r="E28" s="46" t="inlineStr"/>
+      <c r="F28" s="46" t="inlineStr"/>
+      <c r="G28" s="46" t="inlineStr"/>
+      <c r="H28" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I28" s="46" t="inlineStr"/>
+      <c r="J28" s="46" t="inlineStr"/>
+      <c r="K28" s="46" t="inlineStr"/>
+      <c r="L28" s="46" t="inlineStr"/>
+      <c r="M28" s="45" t="n">
+        <v>3200</v>
+      </c>
+      <c r="N28" s="46" t="inlineStr"/>
+      <c r="O28" s="46" t="inlineStr"/>
+      <c r="P28" s="46" t="inlineStr"/>
+      <c r="Q28" s="46" t="inlineStr"/>
+      <c r="R28" s="46" t="inlineStr"/>
+      <c r="S28" s="45" t="n">
+        <v>3200</v>
+      </c>
+      <c r="T28" s="46" t="inlineStr"/>
+      <c r="U28" s="46" t="inlineStr"/>
+      <c r="V28" s="46" t="inlineStr"/>
+      <c r="W28" s="46" t="inlineStr"/>
+      <c r="X28" s="45" t="n">
+        <v>3028</v>
+      </c>
+      <c r="Y28" s="46" t="inlineStr"/>
+      <c r="Z28" s="46" t="inlineStr"/>
+      <c r="AA28" s="46" t="inlineStr"/>
+      <c r="AB28" s="46" t="inlineStr"/>
+      <c r="AC28" s="46" t="inlineStr"/>
+      <c r="AD28" s="46" t="inlineStr"/>
+      <c r="AE28" s="46" t="inlineStr"/>
+      <c r="AF28" s="46" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>V6302</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr"/>
+      <c r="D29" s="46" t="inlineStr"/>
+      <c r="E29" s="46" t="inlineStr"/>
+      <c r="F29" s="46" t="inlineStr"/>
+      <c r="G29" s="46" t="inlineStr"/>
+      <c r="H29" s="45" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I29" s="45" t="n">
+        <v>2250</v>
+      </c>
+      <c r="J29" s="46" t="inlineStr"/>
+      <c r="K29" s="46" t="inlineStr"/>
+      <c r="L29" s="46" t="inlineStr"/>
+      <c r="M29" s="46" t="inlineStr"/>
+      <c r="N29" s="45" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O29" s="46" t="inlineStr"/>
+      <c r="P29" s="46" t="inlineStr"/>
+      <c r="Q29" s="46" t="inlineStr"/>
+      <c r="R29" s="46" t="inlineStr"/>
+      <c r="S29" s="46" t="inlineStr"/>
+      <c r="T29" s="45" t="n">
+        <v>2400</v>
+      </c>
+      <c r="U29" s="46" t="inlineStr"/>
+      <c r="V29" s="46" t="inlineStr"/>
+      <c r="W29" s="46" t="inlineStr"/>
+      <c r="X29" s="46" t="inlineStr"/>
+      <c r="Y29" s="45" t="n">
+        <v>2271</v>
+      </c>
+      <c r="Z29" s="46" t="inlineStr"/>
+      <c r="AA29" s="46" t="inlineStr"/>
+      <c r="AB29" s="46" t="inlineStr"/>
+      <c r="AC29" s="46" t="inlineStr"/>
+      <c r="AD29" s="46" t="inlineStr"/>
+      <c r="AE29" s="46" t="inlineStr"/>
+      <c r="AF29" s="46" t="inlineStr"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
+      </c>
+      <c r="C30" s="45" t="n">
+        <v>650</v>
+      </c>
+      <c r="D30" s="46" t="inlineStr"/>
+      <c r="E30" s="46" t="inlineStr"/>
+      <c r="F30" s="46" t="inlineStr"/>
+      <c r="G30" s="46" t="inlineStr"/>
+      <c r="H30" s="46" t="inlineStr"/>
+      <c r="I30" s="46" t="inlineStr"/>
+      <c r="J30" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="K30" s="45" t="n">
+        <v>750</v>
+      </c>
+      <c r="L30" s="46" t="inlineStr"/>
+      <c r="M30" s="46" t="inlineStr"/>
+      <c r="N30" s="46" t="inlineStr"/>
+      <c r="O30" s="46" t="inlineStr"/>
+      <c r="P30" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q30" s="46" t="inlineStr"/>
+      <c r="R30" s="46" t="inlineStr"/>
+      <c r="S30" s="46" t="inlineStr"/>
+      <c r="T30" s="46" t="inlineStr"/>
+      <c r="U30" s="46" t="inlineStr"/>
+      <c r="V30" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="W30" s="46" t="inlineStr"/>
+      <c r="X30" s="46" t="inlineStr"/>
+      <c r="Y30" s="46" t="inlineStr"/>
+      <c r="Z30" s="46" t="inlineStr"/>
+      <c r="AA30" s="45" t="n">
+        <v>757</v>
+      </c>
+      <c r="AB30" s="46" t="inlineStr"/>
+      <c r="AC30" s="46" t="inlineStr"/>
+      <c r="AD30" s="46" t="inlineStr"/>
+      <c r="AE30" s="46" t="inlineStr"/>
+      <c r="AF30" s="46" t="inlineStr"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>Inventory levels (end of period, realized)</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n"/>
+      <c r="G32" s="42" t="n"/>
+      <c r="H32" s="42" t="n"/>
+      <c r="I32" s="42" t="n"/>
+      <c r="J32" s="42" t="n"/>
+      <c r="K32" s="42" t="n"/>
+      <c r="L32" s="42" t="n"/>
+      <c r="M32" s="42" t="n"/>
+      <c r="N32" s="42" t="n"/>
+      <c r="O32" s="42" t="n"/>
+      <c r="P32" s="42" t="n"/>
+      <c r="Q32" s="42" t="n"/>
+      <c r="R32" s="42" t="n"/>
+      <c r="S32" s="42" t="n"/>
+      <c r="T32" s="42" t="n"/>
+      <c r="U32" s="42" t="n"/>
+      <c r="V32" s="42" t="n"/>
+      <c r="W32" s="42" t="n"/>
+      <c r="X32" s="42" t="n"/>
+      <c r="Y32" s="42" t="n"/>
+      <c r="Z32" s="42" t="n"/>
+      <c r="AA32" s="42" t="n"/>
+      <c r="AB32" s="42" t="n"/>
+      <c r="AC32" s="42" t="n"/>
+      <c r="AD32" s="42" t="n"/>
+      <c r="AE32" s="42" t="n"/>
+      <c r="AF32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G33" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H33" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I33" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K33" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L33" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M33" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N33" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O33" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P33" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q33" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R33" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S33" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T33" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U33" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V33" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W33" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X33" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y33" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z33" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA33" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB33" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC33" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD33" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE33" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF33" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>B1401</t>
+        </is>
+      </c>
+      <c r="C34" s="52" t="n">
+        <v>6400</v>
+      </c>
+      <c r="D34" s="52" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E34" s="52" t="n">
+        <v>6400</v>
+      </c>
+      <c r="F34" s="52" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G34" s="52" t="n">
+        <v>9716</v>
+      </c>
+      <c r="H34" s="52" t="n">
+        <v>1049</v>
+      </c>
+      <c r="I34" s="52" t="n">
+        <v>4382</v>
+      </c>
+      <c r="J34" s="52" t="n">
+        <v>4382</v>
+      </c>
+      <c r="K34" s="52" t="n">
+        <v>7715</v>
+      </c>
+      <c r="L34" s="52" t="n">
+        <v>11048</v>
+      </c>
+      <c r="M34" s="52" t="n">
+        <v>1581</v>
+      </c>
+      <c r="N34" s="52" t="n">
+        <v>1581</v>
+      </c>
+      <c r="O34" s="52" t="n">
+        <v>1581</v>
+      </c>
+      <c r="P34" s="52" t="n">
+        <v>4914</v>
+      </c>
+      <c r="Q34" s="52" t="n">
+        <v>8247</v>
+      </c>
+      <c r="R34" s="52" t="n">
+        <v>11580</v>
+      </c>
+      <c r="S34" s="52" t="n">
+        <v>2113</v>
+      </c>
+      <c r="T34" s="52" t="n">
+        <v>2113</v>
+      </c>
+      <c r="U34" s="52" t="n">
+        <v>2113</v>
+      </c>
+      <c r="V34" s="52" t="n">
+        <v>5446</v>
+      </c>
+      <c r="W34" s="52" t="n">
+        <v>8779</v>
+      </c>
+      <c r="X34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>B2302</t>
+        </is>
+      </c>
+      <c r="C35" s="52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D35" s="52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E35" s="52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F35" s="52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G35" s="52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="52" t="n">
+        <v>4600</v>
+      </c>
+      <c r="M35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="52" t="n">
+        <v>4600</v>
+      </c>
+      <c r="S35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="52" t="n">
+        <v>4084</v>
+      </c>
+      <c r="X35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>B3201</t>
+        </is>
+      </c>
+      <c r="C36" s="52" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D36" s="52" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E36" s="52" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F36" s="52" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G36" s="52" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H36" s="52" t="n">
+        <v>400</v>
+      </c>
+      <c r="I36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>B4702</t>
+        </is>
+      </c>
+      <c r="C37" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D37" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E37" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F37" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G37" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>V1501</t>
+        </is>
+      </c>
+      <c r="C38" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D38" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E38" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F38" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G38" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H38" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I38" s="52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>V6302</t>
+        </is>
+      </c>
+      <c r="C39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
+      </c>
+      <c r="C40" s="52" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D40" s="52" t="n">
+        <v>1728</v>
+      </c>
+      <c r="E40" s="52" t="n">
+        <v>1515</v>
+      </c>
+      <c r="F40" s="52" t="n">
+        <v>1409</v>
+      </c>
+      <c r="G40" s="52" t="n">
+        <v>1261</v>
+      </c>
+      <c r="H40" s="52" t="n">
+        <v>1099</v>
+      </c>
+      <c r="I40" s="52" t="n">
+        <v>732</v>
+      </c>
+      <c r="J40" s="52" t="n">
+        <v>603</v>
+      </c>
+      <c r="K40" s="52" t="n">
+        <v>1293</v>
+      </c>
+      <c r="L40" s="52" t="n">
+        <v>1757</v>
+      </c>
+      <c r="M40" s="52" t="n">
+        <v>1516</v>
+      </c>
+      <c r="N40" s="52" t="n">
+        <v>1304</v>
+      </c>
+      <c r="O40" s="52" t="n">
+        <v>1105</v>
+      </c>
+      <c r="P40" s="52" t="n">
+        <v>869</v>
+      </c>
+      <c r="Q40" s="52" t="n">
+        <v>1482</v>
+      </c>
+      <c r="R40" s="52" t="n">
+        <v>1296</v>
+      </c>
+      <c r="S40" s="52" t="n">
+        <v>1103</v>
+      </c>
+      <c r="T40" s="52" t="n">
+        <v>902</v>
+      </c>
+      <c r="U40" s="52" t="n">
+        <v>674</v>
+      </c>
+      <c r="V40" s="52" t="n">
+        <v>437</v>
+      </c>
+      <c r="W40" s="52" t="n">
+        <v>984</v>
+      </c>
+      <c r="X40" s="52" t="n">
+        <v>775</v>
+      </c>
+      <c r="Y40" s="52" t="n">
+        <v>528</v>
+      </c>
+      <c r="Z40" s="52" t="n">
+        <v>295</v>
+      </c>
+      <c r="AA40" s="52" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB40" s="52" t="n">
+        <v>665</v>
+      </c>
+      <c r="AC40" s="52" t="n">
+        <v>486</v>
+      </c>
+      <c r="AD40" s="52" t="n">
+        <v>315</v>
+      </c>
+      <c r="AE40" s="52" t="n">
+        <v>118</v>
+      </c>
+      <c r="AF40" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>Backorder schedule - E2801 (end product only)</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="n"/>
+      <c r="D42" s="42" t="n"/>
+      <c r="E42" s="42" t="n"/>
+      <c r="F42" s="42" t="n"/>
+      <c r="G42" s="42" t="n"/>
+      <c r="H42" s="42" t="n"/>
+      <c r="I42" s="42" t="n"/>
+      <c r="J42" s="42" t="n"/>
+      <c r="K42" s="42" t="n"/>
+      <c r="L42" s="42" t="n"/>
+      <c r="M42" s="42" t="n"/>
+      <c r="N42" s="42" t="n"/>
+      <c r="O42" s="42" t="n"/>
+      <c r="P42" s="42" t="n"/>
+      <c r="Q42" s="42" t="n"/>
+      <c r="R42" s="42" t="n"/>
+      <c r="S42" s="42" t="n"/>
+      <c r="T42" s="42" t="n"/>
+      <c r="U42" s="42" t="n"/>
+      <c r="V42" s="42" t="n"/>
+      <c r="W42" s="42" t="n"/>
+      <c r="X42" s="42" t="n"/>
+      <c r="Y42" s="42" t="n"/>
+      <c r="Z42" s="42" t="n"/>
+      <c r="AA42" s="42" t="n"/>
+      <c r="AB42" s="42" t="n"/>
+      <c r="AC42" s="42" t="n"/>
+      <c r="AD42" s="42" t="n"/>
+      <c r="AE42" s="42" t="n"/>
+      <c r="AF42" s="42" t="n"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="B43" s="43" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E43" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G43" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H43" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I43" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K43" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L43" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M43" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N43" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O43" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P43" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q43" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R43" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S43" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T43" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U43" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V43" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W43" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X43" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y43" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z43" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA43" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB43" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC43" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD43" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE43" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF43" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
+      </c>
+      <c r="C44" s="46" t="inlineStr"/>
+      <c r="D44" s="46" t="inlineStr"/>
+      <c r="E44" s="46" t="inlineStr"/>
+      <c r="F44" s="46" t="inlineStr"/>
+      <c r="G44" s="46" t="inlineStr"/>
+      <c r="H44" s="46" t="inlineStr"/>
+      <c r="I44" s="46" t="inlineStr"/>
+      <c r="J44" s="46" t="inlineStr"/>
+      <c r="K44" s="46" t="inlineStr"/>
+      <c r="L44" s="46" t="inlineStr"/>
+      <c r="M44" s="46" t="inlineStr"/>
+      <c r="N44" s="46" t="inlineStr"/>
+      <c r="O44" s="46" t="inlineStr"/>
+      <c r="P44" s="46" t="inlineStr"/>
+      <c r="Q44" s="46" t="inlineStr"/>
+      <c r="R44" s="46" t="inlineStr"/>
+      <c r="S44" s="46" t="inlineStr"/>
+      <c r="T44" s="46" t="inlineStr"/>
+      <c r="U44" s="46" t="inlineStr"/>
+      <c r="V44" s="46" t="inlineStr"/>
+      <c r="W44" s="46" t="inlineStr"/>
+      <c r="X44" s="46" t="inlineStr"/>
+      <c r="Y44" s="46" t="inlineStr"/>
+      <c r="Z44" s="46" t="inlineStr"/>
+      <c r="AA44" s="46" t="inlineStr"/>
+      <c r="AB44" s="46" t="inlineStr"/>
+      <c r="AC44" s="46" t="inlineStr"/>
+      <c r="AD44" s="46" t="inlineStr"/>
+      <c r="AE44" s="46" t="inlineStr"/>
+      <c r="AF44" s="55" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>Demand vs delivered (end product)</t>
+        </is>
+      </c>
+      <c r="C46" s="42" t="n"/>
+      <c r="D46" s="42" t="n"/>
+      <c r="E46" s="42" t="n"/>
+      <c r="F46" s="42" t="n"/>
+      <c r="G46" s="42" t="n"/>
+      <c r="H46" s="42" t="n"/>
+      <c r="I46" s="42" t="n"/>
+      <c r="J46" s="42" t="n"/>
+      <c r="K46" s="42" t="n"/>
+      <c r="L46" s="42" t="n"/>
+      <c r="M46" s="42" t="n"/>
+      <c r="N46" s="42" t="n"/>
+      <c r="O46" s="42" t="n"/>
+      <c r="P46" s="42" t="n"/>
+      <c r="Q46" s="42" t="n"/>
+      <c r="R46" s="42" t="n"/>
+      <c r="S46" s="42" t="n"/>
+      <c r="T46" s="42" t="n"/>
+      <c r="U46" s="42" t="n"/>
+      <c r="V46" s="42" t="n"/>
+      <c r="W46" s="42" t="n"/>
+      <c r="X46" s="42" t="n"/>
+      <c r="Y46" s="42" t="n"/>
+      <c r="Z46" s="42" t="n"/>
+      <c r="AA46" s="42" t="n"/>
+      <c r="AB46" s="42" t="n"/>
+      <c r="AC46" s="42" t="n"/>
+      <c r="AD46" s="42" t="n"/>
+      <c r="AE46" s="42" t="n"/>
+      <c r="AF46" s="42" t="n"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="B47" s="43" t="inlineStr"/>
+      <c r="C47" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F47" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G47" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H47" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I47" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J47" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K47" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L47" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M47" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N47" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O47" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P47" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q47" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R47" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S47" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T47" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U47" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V47" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W47" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X47" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y47" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z47" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA47" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB47" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC47" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD47" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE47" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF47" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="C48" s="47" t="n">
+        <v>120</v>
+      </c>
+      <c r="D48" s="47" t="n">
+        <v>152</v>
+      </c>
+      <c r="E48" s="47" t="n">
+        <v>213</v>
+      </c>
+      <c r="F48" s="47" t="n">
+        <v>106</v>
+      </c>
+      <c r="G48" s="47" t="n">
+        <v>148</v>
+      </c>
+      <c r="H48" s="47" t="n">
+        <v>162</v>
+      </c>
+      <c r="I48" s="47" t="n">
+        <v>367</v>
+      </c>
+      <c r="J48" s="47" t="n">
+        <v>129</v>
+      </c>
+      <c r="K48" s="47" t="n">
+        <v>110</v>
+      </c>
+      <c r="L48" s="47" t="n">
+        <v>286</v>
+      </c>
+      <c r="M48" s="47" t="n">
+        <v>241</v>
+      </c>
+      <c r="N48" s="47" t="n">
+        <v>212</v>
+      </c>
+      <c r="O48" s="47" t="n">
+        <v>199</v>
+      </c>
+      <c r="P48" s="47" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q48" s="47" t="n">
+        <v>187</v>
+      </c>
+      <c r="R48" s="47" t="n">
+        <v>186</v>
+      </c>
+      <c r="S48" s="47" t="n">
+        <v>193</v>
+      </c>
+      <c r="T48" s="47" t="n">
+        <v>201</v>
+      </c>
+      <c r="U48" s="47" t="n">
+        <v>228</v>
+      </c>
+      <c r="V48" s="47" t="n">
+        <v>237</v>
+      </c>
+      <c r="W48" s="47" t="n">
+        <v>253</v>
+      </c>
+      <c r="X48" s="47" t="n">
+        <v>209</v>
+      </c>
+      <c r="Y48" s="47" t="n">
+        <v>247</v>
+      </c>
+      <c r="Z48" s="47" t="n">
+        <v>233</v>
+      </c>
+      <c r="AA48" s="47" t="n">
+        <v>195</v>
+      </c>
+      <c r="AB48" s="47" t="n">
+        <v>192</v>
+      </c>
+      <c r="AC48" s="47" t="n">
+        <v>179</v>
+      </c>
+      <c r="AD48" s="47" t="n">
+        <v>171</v>
+      </c>
+      <c r="AE48" s="47" t="n">
+        <v>197</v>
+      </c>
+      <c r="AF48" s="47" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C49" s="47" t="n">
+        <v>120</v>
+      </c>
+      <c r="D49" s="47" t="n">
+        <v>152</v>
+      </c>
+      <c r="E49" s="47" t="n">
+        <v>213</v>
+      </c>
+      <c r="F49" s="47" t="n">
+        <v>106</v>
+      </c>
+      <c r="G49" s="47" t="n">
+        <v>148</v>
+      </c>
+      <c r="H49" s="47" t="n">
+        <v>162</v>
+      </c>
+      <c r="I49" s="47" t="n">
+        <v>367</v>
+      </c>
+      <c r="J49" s="47" t="n">
+        <v>129</v>
+      </c>
+      <c r="K49" s="47" t="n">
+        <v>110</v>
+      </c>
+      <c r="L49" s="47" t="n">
+        <v>286</v>
+      </c>
+      <c r="M49" s="47" t="n">
+        <v>241</v>
+      </c>
+      <c r="N49" s="47" t="n">
+        <v>212</v>
+      </c>
+      <c r="O49" s="47" t="n">
+        <v>199</v>
+      </c>
+      <c r="P49" s="47" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q49" s="47" t="n">
+        <v>187</v>
+      </c>
+      <c r="R49" s="47" t="n">
+        <v>186</v>
+      </c>
+      <c r="S49" s="47" t="n">
+        <v>193</v>
+      </c>
+      <c r="T49" s="47" t="n">
+        <v>201</v>
+      </c>
+      <c r="U49" s="47" t="n">
+        <v>228</v>
+      </c>
+      <c r="V49" s="47" t="n">
+        <v>237</v>
+      </c>
+      <c r="W49" s="47" t="n">
+        <v>253</v>
+      </c>
+      <c r="X49" s="47" t="n">
+        <v>209</v>
+      </c>
+      <c r="Y49" s="47" t="n">
+        <v>247</v>
+      </c>
+      <c r="Z49" s="47" t="n">
+        <v>233</v>
+      </c>
+      <c r="AA49" s="47" t="n">
+        <v>195</v>
+      </c>
+      <c r="AB49" s="47" t="n">
+        <v>192</v>
+      </c>
+      <c r="AC49" s="47" t="n">
+        <v>179</v>
+      </c>
+      <c r="AD49" s="47" t="n">
+        <v>171</v>
+      </c>
+      <c r="AE49" s="47" t="n">
+        <v>197</v>
+      </c>
+      <c r="AF49" s="67" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>Setup decisions</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="n"/>
+      <c r="D51" s="42" t="n"/>
+      <c r="E51" s="42" t="n"/>
+      <c r="F51" s="42" t="n"/>
+      <c r="G51" s="42" t="n"/>
+      <c r="H51" s="42" t="n"/>
+      <c r="I51" s="42" t="n"/>
+      <c r="J51" s="42" t="n"/>
+      <c r="K51" s="42" t="n"/>
+      <c r="L51" s="42" t="n"/>
+      <c r="M51" s="42" t="n"/>
+      <c r="N51" s="42" t="n"/>
+      <c r="O51" s="42" t="n"/>
+      <c r="P51" s="42" t="n"/>
+      <c r="Q51" s="42" t="n"/>
+      <c r="R51" s="42" t="n"/>
+      <c r="S51" s="42" t="n"/>
+      <c r="T51" s="42" t="n"/>
+      <c r="U51" s="42" t="n"/>
+      <c r="V51" s="42" t="n"/>
+      <c r="W51" s="42" t="n"/>
+      <c r="X51" s="42" t="n"/>
+      <c r="Y51" s="42" t="n"/>
+      <c r="Z51" s="42" t="n"/>
+      <c r="AA51" s="42" t="n"/>
+      <c r="AB51" s="42" t="n"/>
+      <c r="AC51" s="42" t="n"/>
+      <c r="AD51" s="42" t="n"/>
+      <c r="AE51" s="42" t="n"/>
+      <c r="AF51" s="42" t="n"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="B52" s="43" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C52" s="43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F52" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G52" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H52" s="43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I52" s="43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" s="43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K52" s="43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L52" s="43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M52" s="43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N52" s="43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O52" s="43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P52" s="43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q52" s="43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R52" s="43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S52" s="43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T52" s="43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U52" s="43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V52" s="43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W52" s="43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X52" s="43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y52" s="43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z52" s="43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA52" s="43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB52" s="43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AC52" s="43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD52" s="43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE52" s="43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF52" s="43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="44" t="inlineStr">
+        <is>
+          <t>B1401</t>
+        </is>
+      </c>
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F53" s="49" t="inlineStr"/>
+      <c r="G53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J53" s="49" t="inlineStr"/>
+      <c r="K53" s="49" t="inlineStr"/>
+      <c r="L53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P53" s="49" t="inlineStr"/>
+      <c r="Q53" s="49" t="inlineStr"/>
+      <c r="R53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T53" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U53" s="49" t="inlineStr"/>
+      <c r="V53" s="49" t="inlineStr"/>
+      <c r="W53" s="49" t="inlineStr"/>
+      <c r="X53" s="49" t="inlineStr"/>
+      <c r="Y53" s="49" t="inlineStr"/>
+      <c r="Z53" s="49" t="inlineStr"/>
+      <c r="AA53" s="49" t="inlineStr"/>
+      <c r="AB53" s="49" t="inlineStr"/>
+      <c r="AC53" s="49" t="inlineStr"/>
+      <c r="AD53" s="49" t="inlineStr"/>
+      <c r="AE53" s="49" t="inlineStr"/>
+      <c r="AF53" s="49" t="inlineStr"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="44" t="inlineStr">
+        <is>
+          <t>B2302</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr"/>
+      <c r="D54" s="49" t="inlineStr"/>
+      <c r="E54" s="49" t="inlineStr"/>
+      <c r="F54" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G54" s="49" t="inlineStr"/>
+      <c r="H54" s="49" t="inlineStr"/>
+      <c r="I54" s="49" t="inlineStr"/>
+      <c r="J54" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K54" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L54" s="49" t="inlineStr"/>
+      <c r="M54" s="49" t="inlineStr"/>
+      <c r="N54" s="49" t="inlineStr"/>
+      <c r="O54" s="49" t="inlineStr"/>
+      <c r="P54" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q54" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R54" s="49" t="inlineStr"/>
+      <c r="S54" s="49" t="inlineStr"/>
+      <c r="T54" s="49" t="inlineStr"/>
+      <c r="U54" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V54" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W54" s="49" t="inlineStr"/>
+      <c r="X54" s="49" t="inlineStr"/>
+      <c r="Y54" s="49" t="inlineStr"/>
+      <c r="Z54" s="49" t="inlineStr"/>
+      <c r="AA54" s="49" t="inlineStr"/>
+      <c r="AB54" s="49" t="inlineStr"/>
+      <c r="AC54" s="49" t="inlineStr"/>
+      <c r="AD54" s="49" t="inlineStr"/>
+      <c r="AE54" s="49" t="inlineStr"/>
+      <c r="AF54" s="49" t="inlineStr"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>B3201</t>
+        </is>
+      </c>
+      <c r="C55" s="49" t="inlineStr"/>
+      <c r="D55" s="49" t="inlineStr"/>
+      <c r="E55" s="49" t="inlineStr"/>
+      <c r="F55" s="49" t="inlineStr"/>
+      <c r="G55" s="49" t="inlineStr"/>
+      <c r="H55" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I55" s="49" t="inlineStr"/>
+      <c r="J55" s="49" t="inlineStr"/>
+      <c r="K55" s="49" t="inlineStr"/>
+      <c r="L55" s="49" t="inlineStr"/>
+      <c r="M55" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N55" s="49" t="inlineStr"/>
+      <c r="O55" s="49" t="inlineStr"/>
+      <c r="P55" s="49" t="inlineStr"/>
+      <c r="Q55" s="49" t="inlineStr"/>
+      <c r="R55" s="49" t="inlineStr"/>
+      <c r="S55" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T55" s="49" t="inlineStr"/>
+      <c r="U55" s="49" t="inlineStr"/>
+      <c r="V55" s="49" t="inlineStr"/>
+      <c r="W55" s="49" t="inlineStr"/>
+      <c r="X55" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y55" s="49" t="inlineStr"/>
+      <c r="Z55" s="49" t="inlineStr"/>
+      <c r="AA55" s="49" t="inlineStr"/>
+      <c r="AB55" s="49" t="inlineStr"/>
+      <c r="AC55" s="49" t="inlineStr"/>
+      <c r="AD55" s="49" t="inlineStr"/>
+      <c r="AE55" s="49" t="inlineStr"/>
+      <c r="AF55" s="49" t="inlineStr"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="B56" s="44" t="inlineStr">
+        <is>
+          <t>B4702</t>
+        </is>
+      </c>
+      <c r="C56" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D56" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr"/>
+      <c r="F56" s="49" t="inlineStr"/>
+      <c r="G56" s="49" t="inlineStr"/>
+      <c r="H56" s="49" t="inlineStr"/>
+      <c r="I56" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J56" s="49" t="inlineStr"/>
+      <c r="K56" s="49" t="inlineStr"/>
+      <c r="L56" s="49" t="inlineStr"/>
+      <c r="M56" s="49" t="inlineStr"/>
+      <c r="N56" s="49" t="inlineStr"/>
+      <c r="O56" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P56" s="49" t="inlineStr"/>
+      <c r="Q56" s="49" t="inlineStr"/>
+      <c r="R56" s="49" t="inlineStr"/>
+      <c r="S56" s="49" t="inlineStr"/>
+      <c r="T56" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U56" s="49" t="inlineStr"/>
+      <c r="V56" s="49" t="inlineStr"/>
+      <c r="W56" s="49" t="inlineStr"/>
+      <c r="X56" s="49" t="inlineStr"/>
+      <c r="Y56" s="49" t="inlineStr"/>
+      <c r="Z56" s="49" t="inlineStr"/>
+      <c r="AA56" s="49" t="inlineStr"/>
+      <c r="AB56" s="49" t="inlineStr"/>
+      <c r="AC56" s="49" t="inlineStr"/>
+      <c r="AD56" s="49" t="inlineStr"/>
+      <c r="AE56" s="49" t="inlineStr"/>
+      <c r="AF56" s="49" t="inlineStr"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="B57" s="44" t="inlineStr">
+        <is>
+          <t>V1501</t>
+        </is>
+      </c>
+      <c r="C57" s="49" t="inlineStr"/>
+      <c r="D57" s="49" t="inlineStr"/>
+      <c r="E57" s="49" t="inlineStr"/>
+      <c r="F57" s="49" t="inlineStr"/>
+      <c r="G57" s="49" t="inlineStr"/>
+      <c r="H57" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I57" s="49" t="inlineStr"/>
+      <c r="J57" s="49" t="inlineStr"/>
+      <c r="K57" s="49" t="inlineStr"/>
+      <c r="L57" s="49" t="inlineStr"/>
+      <c r="M57" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N57" s="49" t="inlineStr"/>
+      <c r="O57" s="49" t="inlineStr"/>
+      <c r="P57" s="49" t="inlineStr"/>
+      <c r="Q57" s="49" t="inlineStr"/>
+      <c r="R57" s="49" t="inlineStr"/>
+      <c r="S57" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T57" s="49" t="inlineStr"/>
+      <c r="U57" s="49" t="inlineStr"/>
+      <c r="V57" s="49" t="inlineStr"/>
+      <c r="W57" s="49" t="inlineStr"/>
+      <c r="X57" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y57" s="49" t="inlineStr"/>
+      <c r="Z57" s="49" t="inlineStr"/>
+      <c r="AA57" s="49" t="inlineStr"/>
+      <c r="AB57" s="49" t="inlineStr"/>
+      <c r="AC57" s="49" t="inlineStr"/>
+      <c r="AD57" s="49" t="inlineStr"/>
+      <c r="AE57" s="49" t="inlineStr"/>
+      <c r="AF57" s="49" t="inlineStr"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>V6302</t>
+        </is>
+      </c>
+      <c r="C58" s="49" t="inlineStr"/>
+      <c r="D58" s="49" t="inlineStr"/>
+      <c r="E58" s="49" t="inlineStr"/>
+      <c r="F58" s="49" t="inlineStr"/>
+      <c r="G58" s="49" t="inlineStr"/>
+      <c r="H58" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I58" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J58" s="49" t="inlineStr"/>
+      <c r="K58" s="49" t="inlineStr"/>
+      <c r="L58" s="49" t="inlineStr"/>
+      <c r="M58" s="49" t="inlineStr"/>
+      <c r="N58" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O58" s="49" t="inlineStr"/>
+      <c r="P58" s="49" t="inlineStr"/>
+      <c r="Q58" s="49" t="inlineStr"/>
+      <c r="R58" s="49" t="inlineStr"/>
+      <c r="S58" s="49" t="inlineStr"/>
+      <c r="T58" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U58" s="49" t="inlineStr"/>
+      <c r="V58" s="49" t="inlineStr"/>
+      <c r="W58" s="49" t="inlineStr"/>
+      <c r="X58" s="49" t="inlineStr"/>
+      <c r="Y58" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z58" s="49" t="inlineStr"/>
+      <c r="AA58" s="49" t="inlineStr"/>
+      <c r="AB58" s="49" t="inlineStr"/>
+      <c r="AC58" s="49" t="inlineStr"/>
+      <c r="AD58" s="49" t="inlineStr"/>
+      <c r="AE58" s="49" t="inlineStr"/>
+      <c r="AF58" s="49" t="inlineStr"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
+      </c>
+      <c r="C59" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D59" s="49" t="inlineStr"/>
+      <c r="E59" s="49" t="inlineStr"/>
+      <c r="F59" s="49" t="inlineStr"/>
+      <c r="G59" s="49" t="inlineStr"/>
+      <c r="H59" s="49" t="inlineStr"/>
+      <c r="I59" s="49" t="inlineStr"/>
+      <c r="J59" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K59" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L59" s="49" t="inlineStr"/>
+      <c r="M59" s="49" t="inlineStr"/>
+      <c r="N59" s="49" t="inlineStr"/>
+      <c r="O59" s="49" t="inlineStr"/>
+      <c r="P59" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q59" s="49" t="inlineStr"/>
+      <c r="R59" s="49" t="inlineStr"/>
+      <c r="S59" s="49" t="inlineStr"/>
+      <c r="T59" s="49" t="inlineStr"/>
+      <c r="U59" s="49" t="inlineStr"/>
+      <c r="V59" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W59" s="49" t="inlineStr"/>
+      <c r="X59" s="49" t="inlineStr"/>
+      <c r="Y59" s="49" t="inlineStr"/>
+      <c r="Z59" s="49" t="inlineStr"/>
+      <c r="AA59" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB59" s="49" t="inlineStr"/>
+      <c r="AC59" s="49" t="inlineStr"/>
+      <c r="AD59" s="49" t="inlineStr"/>
+      <c r="AE59" s="49" t="inlineStr"/>
+      <c r="AF59" s="49" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C3:AF3"/>
+    <mergeCell ref="C4:AF4"/>
+    <mergeCell ref="C6:AF6"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="C11:AF11"/>
+    <mergeCell ref="C10:AF10"/>
+    <mergeCell ref="C5:AF5"/>
+    <mergeCell ref="C9:AF9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/OUTPUT.xlsx
+++ b/OUTPUT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eigenaar\Desktop\Groepswerk\APM-assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FB8A70-1B2C-4FF4-8AE7-938D538580FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B846A8D-0654-4DA1-9C6F-87A816F0C287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="775" firstSheet="25" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="775" firstSheet="23" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Output_1a" sheetId="1" r:id="rId1"/>
@@ -2148,7 +2148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="256">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2738,17 +2738,20 @@
     <xf numFmtId="176" fontId="68" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="60" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2758,6 +2761,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2772,13 +2778,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="46" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
@@ -2787,7 +2787,13 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="172" fontId="47" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="46" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2796,16 +2802,7 @@
     <xf numFmtId="169" fontId="47" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
@@ -2817,7 +2814,13 @@
     <xf numFmtId="174" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="173" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
@@ -2826,31 +2829,31 @@
     <xf numFmtId="164" fontId="28" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="37" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="38" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="38" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="37" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="38" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="175" fontId="37" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2859,22 +2862,22 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="60" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2883,7 +2886,11 @@
     <xf numFmtId="10" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3221,6 +3228,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="nl-BE"/>
               <a:t>Total Cost per X-Expansion Scenario</a:t>
             </a:r>
           </a:p>
@@ -3502,6 +3510,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="nl-BE"/>
                   <a:t>Permanent expansion dx (units)</a:t>
                 </a:r>
               </a:p>
@@ -3539,6 +3548,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="nl-BE"/>
                   <a:t>Total Cost (€)</a:t>
                 </a:r>
               </a:p>
@@ -5096,14 +5106,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>110490</xdr:rowOff>
     </xdr:to>
@@ -5199,16 +5209,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>464820</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>34290</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5587,12 +5597,28 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="210" t="s">
         <v>61</v>
       </c>
       <c r="C1" s="204"/>
@@ -5631,7 +5657,7 @@
       <c r="B3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="208">
+      <c r="C3" s="209">
         <v>394454</v>
       </c>
       <c r="D3" s="204"/>
@@ -5668,7 +5694,7 @@
       <c r="B4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="210">
+      <c r="C4" s="211">
         <v>79500</v>
       </c>
       <c r="D4" s="204"/>
@@ -5705,7 +5731,7 @@
       <c r="B5" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="210">
+      <c r="C5" s="211">
         <v>314954</v>
       </c>
       <c r="D5" s="204"/>
@@ -7389,13 +7415,25 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39"/>
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="212" t="s">
         <v>157</v>
       </c>
       <c r="C1" s="204"/>
@@ -7434,7 +7472,7 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="211">
+      <c r="C3" s="213">
         <v>132000</v>
       </c>
       <c r="D3" s="204"/>
@@ -7471,7 +7509,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="211">
+      <c r="C4" s="213">
         <v>354296.6</v>
       </c>
       <c r="D4" s="204"/>
@@ -7508,7 +7546,7 @@
       <c r="B5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="211">
+      <c r="C5" s="213">
         <v>2000</v>
       </c>
       <c r="D5" s="204"/>
@@ -7545,7 +7583,7 @@
       <c r="B6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="211">
+      <c r="C6" s="213">
         <v>21180</v>
       </c>
       <c r="D6" s="204"/>
@@ -7582,7 +7620,7 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="211">
+      <c r="C7" s="213">
         <v>600</v>
       </c>
       <c r="D7" s="204"/>
@@ -7619,7 +7657,7 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="211">
+      <c r="C8" s="213">
         <v>0</v>
       </c>
       <c r="D8" s="204"/>
@@ -7656,7 +7694,7 @@
       <c r="B9" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="211">
+      <c r="C9" s="213">
         <v>600</v>
       </c>
       <c r="D9" s="204"/>
@@ -7693,7 +7731,7 @@
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="214">
+      <c r="C10" s="216">
         <v>510076.6</v>
       </c>
       <c r="D10" s="204"/>
@@ -7731,7 +7769,7 @@
       <c r="B12" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="213" t="s">
+      <c r="C12" s="215" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="204"/>
@@ -7768,7 +7806,7 @@
       <c r="B13" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C13" s="213" t="s">
+      <c r="C13" s="215" t="s">
         <v>159</v>
       </c>
       <c r="D13" s="204"/>
@@ -7805,7 +7843,7 @@
       <c r="B14" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C14" s="224" t="s">
+      <c r="C14" s="225" t="s">
         <v>161</v>
       </c>
       <c r="D14" s="204"/>
@@ -7842,7 +7880,7 @@
       <c r="B15" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C15" s="213" t="s">
+      <c r="C15" s="215" t="s">
         <v>103</v>
       </c>
       <c r="D15" s="204"/>
@@ -7879,7 +7917,7 @@
       <c r="B16" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="213" t="s">
+      <c r="C16" s="215" t="s">
         <v>105</v>
       </c>
       <c r="D16" s="204"/>
@@ -7916,7 +7954,7 @@
       <c r="B17" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C17" s="213" t="s">
+      <c r="C17" s="215" t="s">
         <v>164</v>
       </c>
       <c r="D17" s="204"/>
@@ -7953,7 +7991,7 @@
       <c r="B18" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="224" t="s">
+      <c r="C18" s="225" t="s">
         <v>166</v>
       </c>
       <c r="D18" s="204"/>
@@ -7990,7 +8028,7 @@
       <c r="B19" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C19" s="213" t="s">
+      <c r="C19" s="215" t="s">
         <v>107</v>
       </c>
       <c r="D19" s="204"/>
@@ -10331,6 +10369,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C15:AF15"/>
     <mergeCell ref="B1:AF1"/>
     <mergeCell ref="C10:AF10"/>
     <mergeCell ref="C16:AF16"/>
@@ -10347,7 +10386,6 @@
     <mergeCell ref="C12:AF12"/>
     <mergeCell ref="C6:AF6"/>
     <mergeCell ref="C7:AF7"/>
-    <mergeCell ref="C15:AF15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10359,12 +10397,31 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="228" t="s">
+      <c r="B1" s="227" t="s">
         <v>169</v>
       </c>
       <c r="C1" s="204"/>
@@ -10403,371 +10460,371 @@
       <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="225">
+      <c r="C3" s="253">
         <v>132000</v>
       </c>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
-      <c r="G3" s="204"/>
-      <c r="H3" s="204"/>
-      <c r="I3" s="204"/>
-      <c r="J3" s="204"/>
-      <c r="K3" s="204"/>
-      <c r="L3" s="204"/>
-      <c r="M3" s="204"/>
-      <c r="N3" s="204"/>
-      <c r="O3" s="204"/>
-      <c r="P3" s="204"/>
-      <c r="Q3" s="204"/>
-      <c r="R3" s="204"/>
-      <c r="S3" s="204"/>
-      <c r="T3" s="204"/>
-      <c r="U3" s="204"/>
-      <c r="V3" s="204"/>
-      <c r="W3" s="204"/>
-      <c r="X3" s="204"/>
-      <c r="Y3" s="204"/>
-      <c r="Z3" s="204"/>
-      <c r="AA3" s="204"/>
-      <c r="AB3" s="204"/>
-      <c r="AC3" s="204"/>
-      <c r="AD3" s="204"/>
-      <c r="AE3" s="204"/>
-      <c r="AF3" s="204"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="254"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
+      <c r="M3" s="254"/>
+      <c r="N3" s="254"/>
+      <c r="O3" s="254"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
+      <c r="AA3" s="254"/>
+      <c r="AB3" s="254"/>
+      <c r="AC3" s="254"/>
+      <c r="AD3" s="254"/>
+      <c r="AE3" s="254"/>
+      <c r="AF3" s="254"/>
     </row>
     <row r="4" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="225">
+      <c r="C4" s="253">
         <v>360656.6</v>
       </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="204"/>
-      <c r="H4" s="204"/>
-      <c r="I4" s="204"/>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="204"/>
-      <c r="W4" s="204"/>
-      <c r="X4" s="204"/>
-      <c r="Y4" s="204"/>
-      <c r="Z4" s="204"/>
-      <c r="AA4" s="204"/>
-      <c r="AB4" s="204"/>
-      <c r="AC4" s="204"/>
-      <c r="AD4" s="204"/>
-      <c r="AE4" s="204"/>
-      <c r="AF4" s="204"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="254"/>
+      <c r="J4" s="254"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="254"/>
+      <c r="N4" s="254"/>
+      <c r="O4" s="254"/>
+      <c r="P4" s="254"/>
+      <c r="Q4" s="254"/>
+      <c r="R4" s="254"/>
+      <c r="S4" s="254"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
+      <c r="AA4" s="254"/>
+      <c r="AB4" s="254"/>
+      <c r="AC4" s="254"/>
+      <c r="AD4" s="254"/>
+      <c r="AE4" s="254"/>
+      <c r="AF4" s="254"/>
     </row>
     <row r="5" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="225">
+      <c r="C5" s="253">
         <v>37250</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="204"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="204"/>
-      <c r="M5" s="204"/>
-      <c r="N5" s="204"/>
-      <c r="O5" s="204"/>
-      <c r="P5" s="204"/>
-      <c r="Q5" s="204"/>
-      <c r="R5" s="204"/>
-      <c r="S5" s="204"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="204"/>
-      <c r="W5" s="204"/>
-      <c r="X5" s="204"/>
-      <c r="Y5" s="204"/>
-      <c r="Z5" s="204"/>
-      <c r="AA5" s="204"/>
-      <c r="AB5" s="204"/>
-      <c r="AC5" s="204"/>
-      <c r="AD5" s="204"/>
-      <c r="AE5" s="204"/>
-      <c r="AF5" s="204"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="254"/>
+      <c r="J5" s="254"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="254"/>
+      <c r="M5" s="254"/>
+      <c r="N5" s="254"/>
+      <c r="O5" s="254"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
+      <c r="AA5" s="254"/>
+      <c r="AB5" s="254"/>
+      <c r="AC5" s="254"/>
+      <c r="AD5" s="254"/>
+      <c r="AE5" s="254"/>
+      <c r="AF5" s="254"/>
     </row>
     <row r="6" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="225">
+      <c r="C6" s="253">
         <v>2000</v>
       </c>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="204"/>
-      <c r="N6" s="204"/>
-      <c r="O6" s="204"/>
-      <c r="P6" s="204"/>
-      <c r="Q6" s="204"/>
-      <c r="R6" s="204"/>
-      <c r="S6" s="204"/>
-      <c r="T6" s="204"/>
-      <c r="U6" s="204"/>
-      <c r="V6" s="204"/>
-      <c r="W6" s="204"/>
-      <c r="X6" s="204"/>
-      <c r="Y6" s="204"/>
-      <c r="Z6" s="204"/>
-      <c r="AA6" s="204"/>
-      <c r="AB6" s="204"/>
-      <c r="AC6" s="204"/>
-      <c r="AD6" s="204"/>
-      <c r="AE6" s="204"/>
-      <c r="AF6" s="204"/>
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
+      <c r="I6" s="254"/>
+      <c r="J6" s="254"/>
+      <c r="K6" s="254"/>
+      <c r="L6" s="254"/>
+      <c r="M6" s="254"/>
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+      <c r="P6" s="254"/>
+      <c r="Q6" s="254"/>
+      <c r="R6" s="254"/>
+      <c r="S6" s="254"/>
+      <c r="T6" s="254"/>
+      <c r="U6" s="254"/>
+      <c r="V6" s="254"/>
+      <c r="W6" s="254"/>
+      <c r="X6" s="254"/>
+      <c r="Y6" s="254"/>
+      <c r="Z6" s="254"/>
+      <c r="AA6" s="254"/>
+      <c r="AB6" s="254"/>
+      <c r="AC6" s="254"/>
+      <c r="AD6" s="254"/>
+      <c r="AE6" s="254"/>
+      <c r="AF6" s="254"/>
     </row>
     <row r="7" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="225">
+      <c r="C7" s="253">
         <v>21180</v>
       </c>
-      <c r="D7" s="204"/>
-      <c r="E7" s="204"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="204"/>
-      <c r="H7" s="204"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="204"/>
-      <c r="K7" s="204"/>
-      <c r="L7" s="204"/>
-      <c r="M7" s="204"/>
-      <c r="N7" s="204"/>
-      <c r="O7" s="204"/>
-      <c r="P7" s="204"/>
-      <c r="Q7" s="204"/>
-      <c r="R7" s="204"/>
-      <c r="S7" s="204"/>
-      <c r="T7" s="204"/>
-      <c r="U7" s="204"/>
-      <c r="V7" s="204"/>
-      <c r="W7" s="204"/>
-      <c r="X7" s="204"/>
-      <c r="Y7" s="204"/>
-      <c r="Z7" s="204"/>
-      <c r="AA7" s="204"/>
-      <c r="AB7" s="204"/>
-      <c r="AC7" s="204"/>
-      <c r="AD7" s="204"/>
-      <c r="AE7" s="204"/>
-      <c r="AF7" s="204"/>
+      <c r="D7" s="254"/>
+      <c r="E7" s="254"/>
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
+      <c r="O7" s="254"/>
+      <c r="P7" s="254"/>
+      <c r="Q7" s="254"/>
+      <c r="R7" s="254"/>
+      <c r="S7" s="254"/>
+      <c r="T7" s="254"/>
+      <c r="U7" s="254"/>
+      <c r="V7" s="254"/>
+      <c r="W7" s="254"/>
+      <c r="X7" s="254"/>
+      <c r="Y7" s="254"/>
+      <c r="Z7" s="254"/>
+      <c r="AA7" s="254"/>
+      <c r="AB7" s="254"/>
+      <c r="AC7" s="254"/>
+      <c r="AD7" s="254"/>
+      <c r="AE7" s="254"/>
+      <c r="AF7" s="254"/>
     </row>
     <row r="8" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="225">
+      <c r="C8" s="253">
         <v>600</v>
       </c>
-      <c r="D8" s="204"/>
-      <c r="E8" s="204"/>
-      <c r="F8" s="204"/>
-      <c r="G8" s="204"/>
-      <c r="H8" s="204"/>
-      <c r="I8" s="204"/>
-      <c r="J8" s="204"/>
-      <c r="K8" s="204"/>
-      <c r="L8" s="204"/>
-      <c r="M8" s="204"/>
-      <c r="N8" s="204"/>
-      <c r="O8" s="204"/>
-      <c r="P8" s="204"/>
-      <c r="Q8" s="204"/>
-      <c r="R8" s="204"/>
-      <c r="S8" s="204"/>
-      <c r="T8" s="204"/>
-      <c r="U8" s="204"/>
-      <c r="V8" s="204"/>
-      <c r="W8" s="204"/>
-      <c r="X8" s="204"/>
-      <c r="Y8" s="204"/>
-      <c r="Z8" s="204"/>
-      <c r="AA8" s="204"/>
-      <c r="AB8" s="204"/>
-      <c r="AC8" s="204"/>
-      <c r="AD8" s="204"/>
-      <c r="AE8" s="204"/>
-      <c r="AF8" s="204"/>
+      <c r="D8" s="254"/>
+      <c r="E8" s="254"/>
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="254"/>
+      <c r="I8" s="254"/>
+      <c r="J8" s="254"/>
+      <c r="K8" s="254"/>
+      <c r="L8" s="254"/>
+      <c r="M8" s="254"/>
+      <c r="N8" s="254"/>
+      <c r="O8" s="254"/>
+      <c r="P8" s="254"/>
+      <c r="Q8" s="254"/>
+      <c r="R8" s="254"/>
+      <c r="S8" s="254"/>
+      <c r="T8" s="254"/>
+      <c r="U8" s="254"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="254"/>
+      <c r="X8" s="254"/>
+      <c r="Y8" s="254"/>
+      <c r="Z8" s="254"/>
+      <c r="AA8" s="254"/>
+      <c r="AB8" s="254"/>
+      <c r="AC8" s="254"/>
+      <c r="AD8" s="254"/>
+      <c r="AE8" s="254"/>
+      <c r="AF8" s="254"/>
     </row>
     <row r="9" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="225">
-        <v>0</v>
-      </c>
-      <c r="D9" s="204"/>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="204"/>
-      <c r="H9" s="204"/>
-      <c r="I9" s="204"/>
-      <c r="J9" s="204"/>
-      <c r="K9" s="204"/>
-      <c r="L9" s="204"/>
-      <c r="M9" s="204"/>
-      <c r="N9" s="204"/>
-      <c r="O9" s="204"/>
-      <c r="P9" s="204"/>
-      <c r="Q9" s="204"/>
-      <c r="R9" s="204"/>
-      <c r="S9" s="204"/>
-      <c r="T9" s="204"/>
-      <c r="U9" s="204"/>
-      <c r="V9" s="204"/>
-      <c r="W9" s="204"/>
-      <c r="X9" s="204"/>
-      <c r="Y9" s="204"/>
-      <c r="Z9" s="204"/>
-      <c r="AA9" s="204"/>
-      <c r="AB9" s="204"/>
-      <c r="AC9" s="204"/>
-      <c r="AD9" s="204"/>
-      <c r="AE9" s="204"/>
-      <c r="AF9" s="204"/>
+      <c r="C9" s="253">
+        <v>0</v>
+      </c>
+      <c r="D9" s="254"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="254"/>
+      <c r="L9" s="254"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="254"/>
+      <c r="O9" s="254"/>
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+      <c r="R9" s="254"/>
+      <c r="S9" s="254"/>
+      <c r="T9" s="254"/>
+      <c r="U9" s="254"/>
+      <c r="V9" s="254"/>
+      <c r="W9" s="254"/>
+      <c r="X9" s="254"/>
+      <c r="Y9" s="254"/>
+      <c r="Z9" s="254"/>
+      <c r="AA9" s="254"/>
+      <c r="AB9" s="254"/>
+      <c r="AC9" s="254"/>
+      <c r="AD9" s="254"/>
+      <c r="AE9" s="254"/>
+      <c r="AF9" s="254"/>
     </row>
     <row r="10" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="C10" s="226">
+      <c r="C10" s="255">
         <v>553686.6</v>
       </c>
-      <c r="D10" s="204"/>
-      <c r="E10" s="204"/>
-      <c r="F10" s="204"/>
-      <c r="G10" s="204"/>
-      <c r="H10" s="204"/>
-      <c r="I10" s="204"/>
-      <c r="J10" s="204"/>
-      <c r="K10" s="204"/>
-      <c r="L10" s="204"/>
-      <c r="M10" s="204"/>
-      <c r="N10" s="204"/>
-      <c r="O10" s="204"/>
-      <c r="P10" s="204"/>
-      <c r="Q10" s="204"/>
-      <c r="R10" s="204"/>
-      <c r="S10" s="204"/>
-      <c r="T10" s="204"/>
-      <c r="U10" s="204"/>
-      <c r="V10" s="204"/>
-      <c r="W10" s="204"/>
-      <c r="X10" s="204"/>
-      <c r="Y10" s="204"/>
-      <c r="Z10" s="204"/>
-      <c r="AA10" s="204"/>
-      <c r="AB10" s="204"/>
-      <c r="AC10" s="204"/>
-      <c r="AD10" s="204"/>
-      <c r="AE10" s="204"/>
-      <c r="AF10" s="204"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="254"/>
+      <c r="I10" s="254"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="254"/>
+      <c r="L10" s="254"/>
+      <c r="M10" s="254"/>
+      <c r="N10" s="254"/>
+      <c r="O10" s="254"/>
+      <c r="P10" s="254"/>
+      <c r="Q10" s="254"/>
+      <c r="R10" s="254"/>
+      <c r="S10" s="254"/>
+      <c r="T10" s="254"/>
+      <c r="U10" s="254"/>
+      <c r="V10" s="254"/>
+      <c r="W10" s="254"/>
+      <c r="X10" s="254"/>
+      <c r="Y10" s="254"/>
+      <c r="Z10" s="254"/>
+      <c r="AA10" s="254"/>
+      <c r="AB10" s="254"/>
+      <c r="AC10" s="254"/>
+      <c r="AD10" s="254"/>
+      <c r="AE10" s="254"/>
+      <c r="AF10" s="254"/>
     </row>
     <row r="11" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="225">
+      <c r="C11" s="253">
         <v>510076.6</v>
       </c>
-      <c r="D11" s="204"/>
-      <c r="E11" s="204"/>
-      <c r="F11" s="204"/>
-      <c r="G11" s="204"/>
-      <c r="H11" s="204"/>
-      <c r="I11" s="204"/>
-      <c r="J11" s="204"/>
-      <c r="K11" s="204"/>
-      <c r="L11" s="204"/>
-      <c r="M11" s="204"/>
-      <c r="N11" s="204"/>
-      <c r="O11" s="204"/>
-      <c r="P11" s="204"/>
-      <c r="Q11" s="204"/>
-      <c r="R11" s="204"/>
-      <c r="S11" s="204"/>
-      <c r="T11" s="204"/>
-      <c r="U11" s="204"/>
-      <c r="V11" s="204"/>
-      <c r="W11" s="204"/>
-      <c r="X11" s="204"/>
-      <c r="Y11" s="204"/>
-      <c r="Z11" s="204"/>
-      <c r="AA11" s="204"/>
-      <c r="AB11" s="204"/>
-      <c r="AC11" s="204"/>
-      <c r="AD11" s="204"/>
-      <c r="AE11" s="204"/>
-      <c r="AF11" s="204"/>
+      <c r="D11" s="254"/>
+      <c r="E11" s="254"/>
+      <c r="F11" s="254"/>
+      <c r="G11" s="254"/>
+      <c r="H11" s="254"/>
+      <c r="I11" s="254"/>
+      <c r="J11" s="254"/>
+      <c r="K11" s="254"/>
+      <c r="L11" s="254"/>
+      <c r="M11" s="254"/>
+      <c r="N11" s="254"/>
+      <c r="O11" s="254"/>
+      <c r="P11" s="254"/>
+      <c r="Q11" s="254"/>
+      <c r="R11" s="254"/>
+      <c r="S11" s="254"/>
+      <c r="T11" s="254"/>
+      <c r="U11" s="254"/>
+      <c r="V11" s="254"/>
+      <c r="W11" s="254"/>
+      <c r="X11" s="254"/>
+      <c r="Y11" s="254"/>
+      <c r="Z11" s="254"/>
+      <c r="AA11" s="254"/>
+      <c r="AB11" s="254"/>
+      <c r="AC11" s="254"/>
+      <c r="AD11" s="254"/>
+      <c r="AE11" s="254"/>
+      <c r="AF11" s="254"/>
     </row>
     <row r="12" spans="2:32" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="229">
+      <c r="C12" s="253">
         <v>43610</v>
       </c>
-      <c r="D12" s="204"/>
-      <c r="E12" s="204"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="204"/>
-      <c r="H12" s="204"/>
-      <c r="I12" s="204"/>
-      <c r="J12" s="204"/>
-      <c r="K12" s="204"/>
-      <c r="L12" s="204"/>
-      <c r="M12" s="204"/>
-      <c r="N12" s="204"/>
-      <c r="O12" s="204"/>
-      <c r="P12" s="204"/>
-      <c r="Q12" s="204"/>
-      <c r="R12" s="204"/>
-      <c r="S12" s="204"/>
-      <c r="T12" s="204"/>
-      <c r="U12" s="204"/>
-      <c r="V12" s="204"/>
-      <c r="W12" s="204"/>
-      <c r="X12" s="204"/>
-      <c r="Y12" s="204"/>
-      <c r="Z12" s="204"/>
-      <c r="AA12" s="204"/>
-      <c r="AB12" s="204"/>
-      <c r="AC12" s="204"/>
-      <c r="AD12" s="204"/>
-      <c r="AE12" s="204"/>
-      <c r="AF12" s="204"/>
+      <c r="D12" s="254"/>
+      <c r="E12" s="254"/>
+      <c r="F12" s="254"/>
+      <c r="G12" s="254"/>
+      <c r="H12" s="254"/>
+      <c r="I12" s="254"/>
+      <c r="J12" s="254"/>
+      <c r="K12" s="254"/>
+      <c r="L12" s="254"/>
+      <c r="M12" s="254"/>
+      <c r="N12" s="254"/>
+      <c r="O12" s="254"/>
+      <c r="P12" s="254"/>
+      <c r="Q12" s="254"/>
+      <c r="R12" s="254"/>
+      <c r="S12" s="254"/>
+      <c r="T12" s="254"/>
+      <c r="U12" s="254"/>
+      <c r="V12" s="254"/>
+      <c r="W12" s="254"/>
+      <c r="X12" s="254"/>
+      <c r="Y12" s="254"/>
+      <c r="Z12" s="254"/>
+      <c r="AA12" s="254"/>
+      <c r="AB12" s="254"/>
+      <c r="AC12" s="254"/>
+      <c r="AD12" s="254"/>
+      <c r="AE12" s="254"/>
+      <c r="AF12" s="254"/>
     </row>
     <row r="13" spans="2:32" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:32" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -10883,7 +10940,7 @@
       <c r="B17" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="227" t="s">
+      <c r="C17" s="226" t="s">
         <v>173</v>
       </c>
       <c r="D17" s="204"/>
@@ -13485,6 +13542,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C17:AF17"/>
+    <mergeCell ref="C8:AF8"/>
+    <mergeCell ref="C4:AF4"/>
+    <mergeCell ref="C12:AF12"/>
+    <mergeCell ref="C6:AF6"/>
+    <mergeCell ref="C7:AF7"/>
+    <mergeCell ref="C15:AF15"/>
     <mergeCell ref="B1:AF1"/>
     <mergeCell ref="C11:AF11"/>
     <mergeCell ref="C10:AF10"/>
@@ -13492,13 +13556,6 @@
     <mergeCell ref="C16:AF16"/>
     <mergeCell ref="C9:AF9"/>
     <mergeCell ref="C3:AF3"/>
-    <mergeCell ref="C17:AF17"/>
-    <mergeCell ref="C8:AF8"/>
-    <mergeCell ref="C4:AF4"/>
-    <mergeCell ref="C12:AF12"/>
-    <mergeCell ref="C6:AF6"/>
-    <mergeCell ref="C7:AF7"/>
-    <mergeCell ref="C15:AF15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13510,8 +13567,21 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -13554,7 +13624,7 @@
       <c r="B3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="232">
+      <c r="C3" s="233">
         <v>132000</v>
       </c>
       <c r="D3" s="204"/>
@@ -13591,7 +13661,7 @@
       <c r="B4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="232">
+      <c r="C4" s="233">
         <v>354296.6</v>
       </c>
       <c r="D4" s="204"/>
@@ -13628,7 +13698,7 @@
       <c r="B5" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="232">
+      <c r="C5" s="233">
         <v>0</v>
       </c>
       <c r="D5" s="204"/>
@@ -13665,7 +13735,7 @@
       <c r="B6" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="232">
+      <c r="C6" s="233">
         <v>0</v>
       </c>
       <c r="D6" s="204"/>
@@ -13702,7 +13772,7 @@
       <c r="B7" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="232">
+      <c r="C7" s="233">
         <v>2000</v>
       </c>
       <c r="D7" s="204"/>
@@ -13739,7 +13809,7 @@
       <c r="B8" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="232">
+      <c r="C8" s="233">
         <v>21180</v>
       </c>
       <c r="D8" s="204"/>
@@ -13776,7 +13846,7 @@
       <c r="B9" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="232">
+      <c r="C9" s="233">
         <v>600</v>
       </c>
       <c r="D9" s="204"/>
@@ -13813,7 +13883,7 @@
       <c r="B10" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="232">
+      <c r="C10" s="233">
         <v>0</v>
       </c>
       <c r="D10" s="204"/>
@@ -13850,7 +13920,7 @@
       <c r="B11" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="232">
+      <c r="C11" s="233">
         <v>0</v>
       </c>
       <c r="D11" s="204"/>
@@ -13887,7 +13957,7 @@
       <c r="B12" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="233">
+      <c r="C12" s="235">
         <v>510076.6</v>
       </c>
       <c r="D12" s="204"/>
@@ -13959,7 +14029,7 @@
       <c r="B15" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="231" t="s">
+      <c r="C15" s="232" t="s">
         <v>185</v>
       </c>
       <c r="D15" s="204"/>
@@ -13996,7 +14066,7 @@
       <c r="B16" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="231" t="s">
+      <c r="C16" s="232" t="s">
         <v>186</v>
       </c>
       <c r="D16" s="204"/>
@@ -14033,7 +14103,7 @@
       <c r="B17" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="231" t="s">
+      <c r="C17" s="232" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="204"/>
@@ -14070,7 +14140,7 @@
       <c r="B18" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="231" t="s">
+      <c r="C18" s="232" t="s">
         <v>189</v>
       </c>
       <c r="D18" s="204"/>
@@ -14107,7 +14177,7 @@
       <c r="B19" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="231" t="s">
+      <c r="C19" s="232" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="204"/>
@@ -14144,7 +14214,7 @@
       <c r="B20" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="C20" s="231" t="s">
+      <c r="C20" s="232" t="s">
         <v>192</v>
       </c>
       <c r="D20" s="204"/>
@@ -14181,7 +14251,7 @@
       <c r="B21" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="231" t="s">
+      <c r="C21" s="232" t="s">
         <v>194</v>
       </c>
       <c r="D21" s="204"/>
@@ -15724,6 +15794,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C12:AF12"/>
+    <mergeCell ref="C6:AF6"/>
     <mergeCell ref="C21:AF21"/>
     <mergeCell ref="C7:AF7"/>
     <mergeCell ref="C15:AF15"/>
@@ -15740,8 +15812,6 @@
     <mergeCell ref="C8:AF8"/>
     <mergeCell ref="C4:AF4"/>
     <mergeCell ref="C20:AF20"/>
-    <mergeCell ref="C12:AF12"/>
-    <mergeCell ref="C6:AF6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15753,8 +15823,21 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -15797,7 +15880,7 @@
       <c r="B3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="232">
+      <c r="C3" s="233">
         <v>129500</v>
       </c>
       <c r="D3" s="204"/>
@@ -15834,7 +15917,7 @@
       <c r="B4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="232">
+      <c r="C4" s="233">
         <v>361468.2</v>
       </c>
       <c r="D4" s="204"/>
@@ -15871,7 +15954,7 @@
       <c r="B5" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="232">
+      <c r="C5" s="233">
         <v>0</v>
       </c>
       <c r="D5" s="204"/>
@@ -15908,7 +15991,7 @@
       <c r="B6" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="232">
+      <c r="C6" s="233">
         <v>0</v>
       </c>
       <c r="D6" s="204"/>
@@ -15945,7 +16028,7 @@
       <c r="B7" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="232">
+      <c r="C7" s="233">
         <v>1000</v>
       </c>
       <c r="D7" s="204"/>
@@ -15982,7 +16065,7 @@
       <c r="B8" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="232">
+      <c r="C8" s="233">
         <v>33780</v>
       </c>
       <c r="D8" s="204"/>
@@ -16019,7 +16102,7 @@
       <c r="B9" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="232">
+      <c r="C9" s="233">
         <v>1084</v>
       </c>
       <c r="D9" s="204"/>
@@ -16056,7 +16139,7 @@
       <c r="B10" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="232">
+      <c r="C10" s="233">
         <v>888</v>
       </c>
       <c r="D10" s="204"/>
@@ -16093,7 +16176,7 @@
       <c r="B11" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="232">
+      <c r="C11" s="233">
         <v>0</v>
       </c>
       <c r="D11" s="204"/>
@@ -16130,7 +16213,7 @@
       <c r="B12" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="233">
+      <c r="C12" s="235">
         <v>527720.19999999995</v>
       </c>
       <c r="D12" s="204"/>
@@ -16202,7 +16285,7 @@
       <c r="B15" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="231" t="s">
+      <c r="C15" s="232" t="s">
         <v>185</v>
       </c>
       <c r="D15" s="204"/>
@@ -16239,7 +16322,7 @@
       <c r="B16" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="231" t="s">
+      <c r="C16" s="232" t="s">
         <v>186</v>
       </c>
       <c r="D16" s="204"/>
@@ -16276,7 +16359,7 @@
       <c r="B17" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="231" t="s">
+      <c r="C17" s="232" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="204"/>
@@ -16313,7 +16396,7 @@
       <c r="B18" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="231" t="s">
+      <c r="C18" s="232" t="s">
         <v>189</v>
       </c>
       <c r="D18" s="204"/>
@@ -16350,7 +16433,7 @@
       <c r="B19" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="231" t="s">
+      <c r="C19" s="232" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="204"/>
@@ -16387,7 +16470,7 @@
       <c r="B20" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="C20" s="231" t="s">
+      <c r="C20" s="232" t="s">
         <v>199</v>
       </c>
       <c r="D20" s="204"/>
@@ -16424,7 +16507,7 @@
       <c r="B21" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="231" t="s">
+      <c r="C21" s="232" t="s">
         <v>200</v>
       </c>
       <c r="D21" s="204"/>
@@ -17965,6 +18048,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C12:AF12"/>
+    <mergeCell ref="C6:AF6"/>
     <mergeCell ref="C21:AF21"/>
     <mergeCell ref="C7:AF7"/>
     <mergeCell ref="C15:AF15"/>
@@ -17981,8 +18066,6 @@
     <mergeCell ref="C8:AF8"/>
     <mergeCell ref="C4:AF4"/>
     <mergeCell ref="C20:AF20"/>
-    <mergeCell ref="C12:AF12"/>
-    <mergeCell ref="C6:AF6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17994,8 +18077,19 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -18038,7 +18132,7 @@
       <c r="B3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="232">
+      <c r="C3" s="233">
         <v>130500</v>
       </c>
       <c r="D3" s="204"/>
@@ -18075,7 +18169,7 @@
       <c r="B4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="232">
+      <c r="C4" s="233">
         <v>273787.8</v>
       </c>
       <c r="D4" s="204"/>
@@ -18112,7 +18206,7 @@
       <c r="B5" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="232">
+      <c r="C5" s="233">
         <v>1250</v>
       </c>
       <c r="D5" s="204"/>
@@ -18149,7 +18243,7 @@
       <c r="B6" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="232">
+      <c r="C6" s="233">
         <v>0</v>
       </c>
       <c r="D6" s="204"/>
@@ -18186,7 +18280,7 @@
       <c r="B7" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="232">
+      <c r="C7" s="233">
         <v>0</v>
       </c>
       <c r="D7" s="204"/>
@@ -18223,7 +18317,7 @@
       <c r="B8" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="232">
+      <c r="C8" s="233">
         <v>10380</v>
       </c>
       <c r="D8" s="204"/>
@@ -18260,7 +18354,7 @@
       <c r="B9" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="232">
+      <c r="C9" s="233">
         <v>364</v>
       </c>
       <c r="D9" s="204"/>
@@ -18297,7 +18391,7 @@
       <c r="B10" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="232">
+      <c r="C10" s="233">
         <v>3432</v>
       </c>
       <c r="D10" s="204"/>
@@ -18334,7 +18428,7 @@
       <c r="B11" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="232">
+      <c r="C11" s="233">
         <v>0</v>
       </c>
       <c r="D11" s="204"/>
@@ -18371,7 +18465,7 @@
       <c r="B12" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="233">
+      <c r="C12" s="235">
         <v>419713.8</v>
       </c>
       <c r="D12" s="204"/>
@@ -18443,7 +18537,7 @@
       <c r="B15" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="231" t="s">
+      <c r="C15" s="232" t="s">
         <v>185</v>
       </c>
       <c r="D15" s="204"/>
@@ -18480,7 +18574,7 @@
       <c r="B16" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="231" t="s">
+      <c r="C16" s="232" t="s">
         <v>186</v>
       </c>
       <c r="D16" s="204"/>
@@ -18517,7 +18611,7 @@
       <c r="B17" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="231" t="s">
+      <c r="C17" s="232" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="204"/>
@@ -18554,7 +18648,7 @@
       <c r="B18" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="231" t="s">
+      <c r="C18" s="232" t="s">
         <v>202</v>
       </c>
       <c r="D18" s="204"/>
@@ -18591,7 +18685,7 @@
       <c r="B19" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="231" t="s">
+      <c r="C19" s="232" t="s">
         <v>203</v>
       </c>
       <c r="D19" s="204"/>
@@ -18628,7 +18722,7 @@
       <c r="B20" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="C20" s="231" t="s">
+      <c r="C20" s="232" t="s">
         <v>204</v>
       </c>
       <c r="D20" s="204"/>
@@ -18665,7 +18759,7 @@
       <c r="B21" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="231" t="s">
+      <c r="C21" s="232" t="s">
         <v>205</v>
       </c>
       <c r="D21" s="204"/>
@@ -20214,6 +20308,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C12:AF12"/>
+    <mergeCell ref="C6:AF6"/>
     <mergeCell ref="C21:AF21"/>
     <mergeCell ref="C7:AF7"/>
     <mergeCell ref="C15:AF15"/>
@@ -20230,8 +20326,6 @@
     <mergeCell ref="C8:AF8"/>
     <mergeCell ref="C4:AF4"/>
     <mergeCell ref="C20:AF20"/>
-    <mergeCell ref="C12:AF12"/>
-    <mergeCell ref="C6:AF6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20243,8 +20337,19 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20287,7 +20392,7 @@
       <c r="B3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="232">
+      <c r="C3" s="233">
         <v>130500</v>
       </c>
       <c r="D3" s="204"/>
@@ -20324,7 +20429,7 @@
       <c r="B4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="232">
+      <c r="C4" s="233">
         <v>278735.40000000002</v>
       </c>
       <c r="D4" s="204"/>
@@ -20361,7 +20466,7 @@
       <c r="B5" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="232">
+      <c r="C5" s="233">
         <v>1250</v>
       </c>
       <c r="D5" s="204"/>
@@ -20398,7 +20503,7 @@
       <c r="B6" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="232">
+      <c r="C6" s="233">
         <v>0</v>
       </c>
       <c r="D6" s="204"/>
@@ -20435,7 +20540,7 @@
       <c r="B7" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="232">
+      <c r="C7" s="233">
         <v>0</v>
       </c>
       <c r="D7" s="204"/>
@@ -20472,7 +20577,7 @@
       <c r="B8" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="232">
+      <c r="C8" s="233">
         <v>27660</v>
       </c>
       <c r="D8" s="204"/>
@@ -20509,7 +20614,7 @@
       <c r="B9" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="232">
+      <c r="C9" s="233">
         <v>748</v>
       </c>
       <c r="D9" s="204"/>
@@ -20546,7 +20651,7 @@
       <c r="B10" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="232">
+      <c r="C10" s="233">
         <v>24</v>
       </c>
       <c r="D10" s="204"/>
@@ -20583,7 +20688,7 @@
       <c r="B11" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="232">
+      <c r="C11" s="233">
         <v>0</v>
       </c>
       <c r="D11" s="204"/>
@@ -20620,7 +20725,7 @@
       <c r="B12" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="233">
+      <c r="C12" s="235">
         <v>438917.4</v>
       </c>
       <c r="D12" s="204"/>
@@ -20692,7 +20797,7 @@
       <c r="B15" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="231" t="s">
+      <c r="C15" s="232" t="s">
         <v>185</v>
       </c>
       <c r="D15" s="204"/>
@@ -20729,7 +20834,7 @@
       <c r="B16" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="231" t="s">
+      <c r="C16" s="232" t="s">
         <v>186</v>
       </c>
       <c r="D16" s="204"/>
@@ -20766,7 +20871,7 @@
       <c r="B17" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="231" t="s">
+      <c r="C17" s="232" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="204"/>
@@ -20803,7 +20908,7 @@
       <c r="B18" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="231" t="s">
+      <c r="C18" s="232" t="s">
         <v>202</v>
       </c>
       <c r="D18" s="204"/>
@@ -20840,7 +20945,7 @@
       <c r="B19" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="231" t="s">
+      <c r="C19" s="232" t="s">
         <v>208</v>
       </c>
       <c r="D19" s="204"/>
@@ -20877,7 +20982,7 @@
       <c r="B20" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="C20" s="231" t="s">
+      <c r="C20" s="232" t="s">
         <v>204</v>
       </c>
       <c r="D20" s="204"/>
@@ -20914,7 +21019,7 @@
       <c r="B21" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="231" t="s">
+      <c r="C21" s="232" t="s">
         <v>209</v>
       </c>
       <c r="D21" s="204"/>
@@ -22463,6 +22568,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C12:AF12"/>
+    <mergeCell ref="C6:AF6"/>
     <mergeCell ref="C21:AF21"/>
     <mergeCell ref="C7:AF7"/>
     <mergeCell ref="C15:AF15"/>
@@ -22479,8 +22586,6 @@
     <mergeCell ref="C8:AF8"/>
     <mergeCell ref="C4:AF4"/>
     <mergeCell ref="C20:AF20"/>
-    <mergeCell ref="C12:AF12"/>
-    <mergeCell ref="C6:AF6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22844,12 +22949,27 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="16" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="239" t="s">
+      <c r="B1" s="238" t="s">
         <v>225</v>
       </c>
       <c r="C1" s="204"/>
@@ -22888,7 +23008,7 @@
       <c r="B3" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="235">
+      <c r="C3" s="236">
         <v>130500</v>
       </c>
       <c r="D3" s="204"/>
@@ -22925,7 +23045,7 @@
       <c r="B4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="235">
+      <c r="C4" s="236">
         <v>273787.8</v>
       </c>
       <c r="D4" s="204"/>
@@ -22962,7 +23082,7 @@
       <c r="B5" s="82" t="s">
         <v>226</v>
       </c>
-      <c r="C5" s="235">
+      <c r="C5" s="236">
         <v>2500</v>
       </c>
       <c r="D5" s="204"/>
@@ -22999,7 +23119,7 @@
       <c r="B6" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="235">
+      <c r="C6" s="236">
         <v>0</v>
       </c>
       <c r="D6" s="204"/>
@@ -23036,7 +23156,7 @@
       <c r="B7" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="235">
+      <c r="C7" s="236">
         <v>10380</v>
       </c>
       <c r="D7" s="204"/>
@@ -23073,7 +23193,7 @@
       <c r="B8" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="235">
+      <c r="C8" s="236">
         <v>364</v>
       </c>
       <c r="D8" s="204"/>
@@ -23110,7 +23230,7 @@
       <c r="B9" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="235">
+      <c r="C9" s="236">
         <v>3432</v>
       </c>
       <c r="D9" s="204"/>
@@ -23147,7 +23267,7 @@
       <c r="B10" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="235">
+      <c r="C10" s="236">
         <v>3796</v>
       </c>
       <c r="D10" s="204"/>
@@ -23184,7 +23304,7 @@
       <c r="B11" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="238">
+      <c r="C11" s="240">
         <v>420963.8</v>
       </c>
       <c r="D11" s="204"/>
@@ -23333,7 +23453,7 @@
       <c r="B16" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="236" t="s">
+      <c r="C16" s="239" t="s">
         <v>73</v>
       </c>
       <c r="D16" s="204"/>
@@ -23370,7 +23490,7 @@
       <c r="B17" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="236" t="s">
+      <c r="C17" s="239" t="s">
         <v>233</v>
       </c>
       <c r="D17" s="204"/>
@@ -23444,7 +23564,7 @@
       <c r="B19" s="82" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="236" t="s">
+      <c r="C19" s="239" t="s">
         <v>103</v>
       </c>
       <c r="D19" s="204"/>
@@ -23481,7 +23601,7 @@
       <c r="B20" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="236" t="s">
+      <c r="C20" s="239" t="s">
         <v>105</v>
       </c>
       <c r="D20" s="204"/>
@@ -23518,7 +23638,7 @@
       <c r="B21" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="236" t="s">
+      <c r="C21" s="239" t="s">
         <v>234</v>
       </c>
       <c r="D21" s="204"/>
@@ -23592,7 +23712,7 @@
       <c r="B23" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="236" t="s">
+      <c r="C23" s="239" t="s">
         <v>107</v>
       </c>
       <c r="D23" s="204"/>
@@ -25957,12 +26077,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C3:AF3"/>
-    <mergeCell ref="C6:AF6"/>
-    <mergeCell ref="C15:AF15"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="C5:AF5"/>
-    <mergeCell ref="C14:AF14"/>
     <mergeCell ref="C23:AF23"/>
     <mergeCell ref="C17:AF17"/>
     <mergeCell ref="C8:AF8"/>
@@ -25970,7 +26084,6 @@
     <mergeCell ref="C19:AF19"/>
     <mergeCell ref="C13:AF13"/>
     <mergeCell ref="C18:AF18"/>
-    <mergeCell ref="C4:AF4"/>
     <mergeCell ref="C20:AF20"/>
     <mergeCell ref="C10:AF10"/>
     <mergeCell ref="C16:AF16"/>
@@ -25978,6 +26091,13 @@
     <mergeCell ref="C9:AF9"/>
     <mergeCell ref="C21:AF21"/>
     <mergeCell ref="C11:AF11"/>
+    <mergeCell ref="C3:AF3"/>
+    <mergeCell ref="C6:AF6"/>
+    <mergeCell ref="C15:AF15"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="C5:AF5"/>
+    <mergeCell ref="C14:AF14"/>
+    <mergeCell ref="C4:AF4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25989,12 +26109,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="6" width="14" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="239" t="s">
+      <c r="B1" s="238" t="s">
         <v>238</v>
       </c>
       <c r="C1" s="204"/>
@@ -26255,12 +26375,23 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="239" t="s">
+      <c r="B1" s="238" t="s">
         <v>245</v>
       </c>
       <c r="C1" s="204"/>
@@ -26299,7 +26430,7 @@
       <c r="B3" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="240">
+      <c r="C3" s="242">
         <v>130500</v>
       </c>
       <c r="D3" s="204"/>
@@ -26336,7 +26467,7 @@
       <c r="B4" s="82" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="240">
+      <c r="C4" s="242">
         <v>2500</v>
       </c>
       <c r="D4" s="204"/>
@@ -26373,7 +26504,7 @@
       <c r="B5" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="240">
+      <c r="C5" s="242">
         <v>280147.8</v>
       </c>
       <c r="D5" s="204"/>
@@ -26410,7 +26541,7 @@
       <c r="B6" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="240">
+      <c r="C6" s="242">
         <v>37250</v>
       </c>
       <c r="D6" s="204"/>
@@ -26447,7 +26578,7 @@
       <c r="B7" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="240">
+      <c r="C7" s="242">
         <v>0</v>
       </c>
       <c r="D7" s="204"/>
@@ -26484,7 +26615,7 @@
       <c r="B8" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="240">
+      <c r="C8" s="242">
         <v>10380</v>
       </c>
       <c r="D8" s="204"/>
@@ -26521,7 +26652,7 @@
       <c r="B9" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="240">
+      <c r="C9" s="242">
         <v>364</v>
       </c>
       <c r="D9" s="204"/>
@@ -26558,7 +26689,7 @@
       <c r="B10" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="240">
+      <c r="C10" s="242">
         <v>3432</v>
       </c>
       <c r="D10" s="204"/>
@@ -26632,7 +26763,7 @@
       <c r="B12" s="82" t="s">
         <v>247</v>
       </c>
-      <c r="C12" s="240">
+      <c r="C12" s="242">
         <v>420963.8</v>
       </c>
       <c r="D12" s="204"/>
@@ -26669,7 +26800,7 @@
       <c r="B13" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="243">
         <v>43610</v>
       </c>
       <c r="D13" s="204"/>
@@ -26742,7 +26873,7 @@
       <c r="B16" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="236" t="s">
+      <c r="C16" s="239" t="s">
         <v>67</v>
       </c>
       <c r="D16" s="204"/>
@@ -26779,7 +26910,7 @@
       <c r="B17" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="236" t="s">
+      <c r="C17" s="239" t="s">
         <v>172</v>
       </c>
       <c r="D17" s="204"/>
@@ -26816,7 +26947,7 @@
       <c r="B18" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="243" t="s">
+      <c r="C18" s="244" t="s">
         <v>173</v>
       </c>
       <c r="D18" s="204"/>
@@ -26853,7 +26984,7 @@
       <c r="B19" s="82" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="236" t="s">
+      <c r="C19" s="239" t="s">
         <v>202</v>
       </c>
       <c r="D19" s="204"/>
@@ -29323,12 +29454,28 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="212" t="s">
         <v>62</v>
       </c>
       <c r="C1" s="204"/>
@@ -29367,7 +29514,7 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="211">
+      <c r="C3" s="213">
         <v>79500</v>
       </c>
       <c r="D3" s="204"/>
@@ -29404,7 +29551,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="211">
+      <c r="C4" s="213">
         <v>321542</v>
       </c>
       <c r="D4" s="204"/>
@@ -29441,7 +29588,7 @@
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="211">
+      <c r="C5" s="213">
         <v>46750</v>
       </c>
       <c r="D5" s="204"/>
@@ -29478,7 +29625,7 @@
       <c r="B6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="214">
+      <c r="C6" s="216">
         <v>447792</v>
       </c>
       <c r="D6" s="204"/>
@@ -29515,7 +29662,7 @@
       <c r="B7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="211">
+      <c r="C7" s="213">
         <v>394454</v>
       </c>
       <c r="D7" s="204"/>
@@ -29552,7 +29699,7 @@
       <c r="B8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="212">
+      <c r="C8" s="214">
         <v>53338</v>
       </c>
       <c r="D8" s="204"/>
@@ -29625,7 +29772,7 @@
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="213" t="s">
+      <c r="C11" s="215" t="s">
         <v>67</v>
       </c>
       <c r="D11" s="204"/>
@@ -29662,7 +29809,7 @@
       <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="213" t="s">
+      <c r="C12" s="215" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="204"/>
@@ -31499,15 +31646,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C12:AF12"/>
+    <mergeCell ref="C6:AF6"/>
+    <mergeCell ref="C7:AF7"/>
+    <mergeCell ref="C11:AF11"/>
     <mergeCell ref="B1:AF1"/>
     <mergeCell ref="C5:AF5"/>
     <mergeCell ref="C3:AF3"/>
     <mergeCell ref="C8:AF8"/>
     <mergeCell ref="C4:AF4"/>
-    <mergeCell ref="C12:AF12"/>
-    <mergeCell ref="C6:AF6"/>
-    <mergeCell ref="C7:AF7"/>
-    <mergeCell ref="C11:AF11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31524,7 +31671,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="239" t="s">
+      <c r="B1" s="238" t="s">
         <v>250</v>
       </c>
       <c r="C1" s="204"/>
@@ -31870,17 +32017,24 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="32" width="8" customWidth="1"/>
-    <col min="33" max="33" width="12" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="27" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="245" t="s">
         <v>257</v>
       </c>
       <c r="C1" s="204"/>
@@ -31893,7 +32047,7 @@
       <c r="J1" s="204"/>
     </row>
     <row r="2" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="246" t="s">
         <v>258</v>
       </c>
       <c r="C2" s="204"/>
@@ -33420,17 +33574,26 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="32" width="8" customWidth="1"/>
-    <col min="33" max="33" width="12" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="23" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="245" t="s">
         <v>324</v>
       </c>
       <c r="C1" s="204"/>
@@ -33443,7 +33606,7 @@
       <c r="J1" s="204"/>
     </row>
     <row r="2" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="246" t="s">
         <v>325</v>
       </c>
       <c r="C2" s="204"/>
@@ -35605,12 +35768,28 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="245" t="s">
         <v>381</v>
       </c>
       <c r="C1" s="204"/>
@@ -35648,7 +35827,7 @@
       <c r="B3" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="203">
+      <c r="C3" s="250">
         <v>132000</v>
       </c>
       <c r="D3" s="204"/>
@@ -35685,7 +35864,7 @@
       <c r="B4" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="203">
+      <c r="C4" s="250">
         <v>365048.6</v>
       </c>
       <c r="D4" s="204"/>
@@ -35722,7 +35901,7 @@
       <c r="B5" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="203">
+      <c r="C5" s="250">
         <v>12500</v>
       </c>
       <c r="D5" s="204"/>
@@ -35759,7 +35938,7 @@
       <c r="B6" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="203">
+      <c r="C6" s="250">
         <v>2000</v>
       </c>
       <c r="D6" s="204"/>
@@ -35796,7 +35975,7 @@
       <c r="B7" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="203">
+      <c r="C7" s="250">
         <v>26580</v>
       </c>
       <c r="D7" s="204"/>
@@ -35833,7 +36012,7 @@
       <c r="B8" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="203">
+      <c r="C8" s="250">
         <v>600</v>
       </c>
       <c r="D8" s="204"/>
@@ -35870,7 +36049,7 @@
       <c r="B9" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="203">
+      <c r="C9" s="250">
         <v>0</v>
       </c>
       <c r="D9" s="204"/>
@@ -35907,7 +36086,7 @@
       <c r="B10" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="207">
+      <c r="C10" s="248">
         <v>538728.6</v>
       </c>
       <c r="D10" s="204"/>
@@ -35979,7 +36158,7 @@
       <c r="B13" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="205" t="s">
+      <c r="C13" s="249" t="s">
         <v>383</v>
       </c>
       <c r="D13" s="204"/>
@@ -36016,7 +36195,7 @@
       <c r="B14" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="205" t="s">
+      <c r="C14" s="249" t="s">
         <v>384</v>
       </c>
       <c r="D14" s="204"/>
@@ -36053,7 +36232,7 @@
       <c r="B15" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="245" t="s">
+      <c r="C15" s="247" t="s">
         <v>385</v>
       </c>
       <c r="D15" s="204"/>
@@ -36090,7 +36269,7 @@
       <c r="B16" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="205" t="s">
+      <c r="C16" s="249" t="s">
         <v>386</v>
       </c>
       <c r="D16" s="204"/>
@@ -38339,12 +38518,28 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="245" t="s">
         <v>387</v>
       </c>
       <c r="C1" s="204"/>
@@ -38382,7 +38577,7 @@
       <c r="B3" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="203">
+      <c r="C3" s="250">
         <v>132000</v>
       </c>
       <c r="D3" s="204"/>
@@ -38419,7 +38614,7 @@
       <c r="B4" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="203">
+      <c r="C4" s="250">
         <v>366899</v>
       </c>
       <c r="D4" s="204"/>
@@ -38456,7 +38651,7 @@
       <c r="B5" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="203">
+      <c r="C5" s="250">
         <v>6500</v>
       </c>
       <c r="D5" s="204"/>
@@ -38493,7 +38688,7 @@
       <c r="B6" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="203">
+      <c r="C6" s="250">
         <v>2000</v>
       </c>
       <c r="D6" s="204"/>
@@ -38530,7 +38725,7 @@
       <c r="B7" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="203">
+      <c r="C7" s="250">
         <v>28740</v>
       </c>
       <c r="D7" s="204"/>
@@ -38567,7 +38762,7 @@
       <c r="B8" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="203">
+      <c r="C8" s="250">
         <v>600</v>
       </c>
       <c r="D8" s="204"/>
@@ -38604,7 +38799,7 @@
       <c r="B9" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="203">
+      <c r="C9" s="250">
         <v>0</v>
       </c>
       <c r="D9" s="204"/>
@@ -38641,7 +38836,7 @@
       <c r="B10" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="207">
+      <c r="C10" s="248">
         <v>536739</v>
       </c>
       <c r="D10" s="204"/>
@@ -38713,7 +38908,7 @@
       <c r="B13" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="205" t="s">
+      <c r="C13" s="249" t="s">
         <v>383</v>
       </c>
       <c r="D13" s="204"/>
@@ -38750,7 +38945,7 @@
       <c r="B14" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="205" t="s">
+      <c r="C14" s="249" t="s">
         <v>389</v>
       </c>
       <c r="D14" s="204"/>
@@ -38787,7 +38982,7 @@
       <c r="B15" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="245" t="s">
+      <c r="C15" s="247" t="s">
         <v>390</v>
       </c>
       <c r="D15" s="204"/>
@@ -38824,7 +39019,7 @@
       <c r="B16" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="205" t="s">
+      <c r="C16" s="249" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="204"/>
@@ -41078,7 +41273,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="245" t="s">
         <v>391</v>
       </c>
       <c r="C1" s="204"/>
@@ -41116,7 +41311,7 @@
       <c r="B3" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="203">
+      <c r="C3" s="250">
         <v>132000</v>
       </c>
       <c r="D3" s="204"/>
@@ -41153,7 +41348,7 @@
       <c r="B4" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="203">
+      <c r="C4" s="250">
         <v>359282.6</v>
       </c>
       <c r="D4" s="204"/>
@@ -41190,7 +41385,7 @@
       <c r="B5" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="203">
+      <c r="C5" s="250">
         <v>0</v>
       </c>
       <c r="D5" s="204"/>
@@ -41227,7 +41422,7 @@
       <c r="B6" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="203">
+      <c r="C6" s="250">
         <v>2000</v>
       </c>
       <c r="D6" s="204"/>
@@ -41264,7 +41459,7 @@
       <c r="B7" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="203">
+      <c r="C7" s="250">
         <v>26580</v>
       </c>
       <c r="D7" s="204"/>
@@ -41301,7 +41496,7 @@
       <c r="B8" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="203">
+      <c r="C8" s="250">
         <v>600</v>
       </c>
       <c r="D8" s="204"/>
@@ -41338,7 +41533,7 @@
       <c r="B9" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="203">
+      <c r="C9" s="250">
         <v>0</v>
       </c>
       <c r="D9" s="204"/>
@@ -41375,7 +41570,7 @@
       <c r="B10" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="207">
+      <c r="C10" s="248">
         <v>520462.6</v>
       </c>
       <c r="D10" s="204"/>
@@ -41447,7 +41642,7 @@
       <c r="B13" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="205" t="s">
+      <c r="C13" s="249" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="204"/>
@@ -41484,7 +41679,7 @@
       <c r="B14" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="205" t="s">
+      <c r="C14" s="249" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="204"/>
@@ -41521,7 +41716,7 @@
       <c r="B15" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="205" t="s">
+      <c r="C15" s="249" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="204"/>
@@ -41558,7 +41753,7 @@
       <c r="B16" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="205" t="s">
+      <c r="C16" s="249" t="s">
         <v>386</v>
       </c>
       <c r="D16" s="204"/>
@@ -43487,12 +43682,28 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="245" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="204"/>
@@ -43530,7 +43741,7 @@
       <c r="B3" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="203">
+      <c r="C3" s="250">
         <v>132000</v>
       </c>
       <c r="D3" s="204"/>
@@ -43567,7 +43778,7 @@
       <c r="B4" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="203">
+      <c r="C4" s="250">
         <v>361277</v>
       </c>
       <c r="D4" s="204"/>
@@ -43604,7 +43815,7 @@
       <c r="B5" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="203">
+      <c r="C5" s="250">
         <v>0</v>
       </c>
       <c r="D5" s="204"/>
@@ -43641,7 +43852,7 @@
       <c r="B6" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="203">
+      <c r="C6" s="250">
         <v>2000</v>
       </c>
       <c r="D6" s="204"/>
@@ -43678,7 +43889,7 @@
       <c r="B7" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="203">
+      <c r="C7" s="250">
         <v>28740</v>
       </c>
       <c r="D7" s="204"/>
@@ -43715,7 +43926,7 @@
       <c r="B8" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="203">
+      <c r="C8" s="250">
         <v>600</v>
       </c>
       <c r="D8" s="204"/>
@@ -43752,7 +43963,7 @@
       <c r="B9" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="203">
+      <c r="C9" s="250">
         <v>0</v>
       </c>
       <c r="D9" s="204"/>
@@ -43789,7 +44000,7 @@
       <c r="B10" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="207">
+      <c r="C10" s="248">
         <v>524617</v>
       </c>
       <c r="D10" s="204"/>
@@ -43861,7 +44072,7 @@
       <c r="B13" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="205" t="s">
+      <c r="C13" s="249" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="204"/>
@@ -43898,7 +44109,7 @@
       <c r="B14" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="205" t="s">
+      <c r="C14" s="249" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="204"/>
@@ -43935,7 +44146,7 @@
       <c r="B15" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="205" t="s">
+      <c r="C15" s="249" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="204"/>
@@ -43972,7 +44183,7 @@
       <c r="B16" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="205" t="s">
+      <c r="C16" s="249" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="204"/>
@@ -45901,32 +46112,32 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="40.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="248" t="s">
+      <c r="B1" s="208" t="s">
         <v>393</v>
       </c>
       <c r="C1" s="204"/>
@@ -45970,7 +46181,7 @@
       <c r="B3" s="169" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="247">
+      <c r="C3" s="206">
         <v>162000</v>
       </c>
       <c r="D3" s="204"/>
@@ -46012,7 +46223,7 @@
       <c r="B4" s="169" t="s">
         <v>395</v>
       </c>
-      <c r="C4" s="247">
+      <c r="C4" s="206">
         <v>369375.7</v>
       </c>
       <c r="D4" s="204"/>
@@ -46054,7 +46265,7 @@
       <c r="B5" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="247">
+      <c r="C5" s="206">
         <v>1000</v>
       </c>
       <c r="D5" s="204"/>
@@ -46096,7 +46307,7 @@
       <c r="B6" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="247">
+      <c r="C6" s="206">
         <v>45435</v>
       </c>
       <c r="D6" s="204"/>
@@ -46138,7 +46349,7 @@
       <c r="B7" s="169" t="s">
         <v>396</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="206">
         <v>1372</v>
       </c>
       <c r="D7" s="204"/>
@@ -46180,7 +46391,7 @@
       <c r="B8" s="169" t="s">
         <v>397</v>
       </c>
-      <c r="C8" s="247">
+      <c r="C8" s="206">
         <v>3194</v>
       </c>
       <c r="D8" s="204"/>
@@ -46222,7 +46433,7 @@
       <c r="B9" s="169" t="s">
         <v>398</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="206">
         <v>4566</v>
       </c>
       <c r="D9" s="204"/>
@@ -46264,7 +46475,7 @@
       <c r="B10" s="169" t="s">
         <v>399</v>
       </c>
-      <c r="C10" s="246">
+      <c r="C10" s="205">
         <v>582376.69999999995</v>
       </c>
       <c r="D10" s="204"/>
@@ -46311,7 +46522,7 @@
       <c r="B13" s="169" t="s">
         <v>401</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="206">
         <v>138857.14000000001</v>
       </c>
       <c r="D13" s="204"/>
@@ -46353,7 +46564,7 @@
       <c r="B14" s="169" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="247">
+      <c r="C14" s="206">
         <v>316607.74</v>
       </c>
       <c r="D14" s="204"/>
@@ -46395,7 +46606,7 @@
       <c r="B15" s="169" t="s">
         <v>403</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="206">
         <v>1176</v>
       </c>
       <c r="D15" s="204"/>
@@ -46437,7 +46648,7 @@
       <c r="B16" s="169" t="s">
         <v>404</v>
       </c>
-      <c r="C16" s="247">
+      <c r="C16" s="206">
         <v>2737.71</v>
       </c>
       <c r="D16" s="204"/>
@@ -46479,7 +46690,7 @@
       <c r="B17" s="169" t="s">
         <v>405</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="206">
         <v>1000</v>
       </c>
       <c r="D17" s="204"/>
@@ -46521,7 +46732,7 @@
       <c r="B18" s="169" t="s">
         <v>406</v>
       </c>
-      <c r="C18" s="247">
+      <c r="C18" s="206">
         <v>45435</v>
       </c>
       <c r="D18" s="204"/>
@@ -46563,7 +46774,7 @@
       <c r="B19" s="169" t="s">
         <v>407</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="205">
         <v>505813.6</v>
       </c>
       <c r="D19" s="204"/>
@@ -46610,7 +46821,7 @@
       <c r="B22" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="251">
+      <c r="C22" s="252">
         <v>1</v>
       </c>
       <c r="D22" s="204"/>
@@ -46652,7 +46863,7 @@
       <c r="B23" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="251">
+      <c r="C23" s="252">
         <v>1</v>
       </c>
       <c r="D23" s="204"/>
@@ -46871,7 +47082,7 @@
       <c r="B38" s="169" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="249" t="s">
+      <c r="C38" s="207" t="s">
         <v>73</v>
       </c>
       <c r="D38" s="204"/>
@@ -46913,7 +47124,7 @@
       <c r="B39" s="169" t="s">
         <v>158</v>
       </c>
-      <c r="C39" s="249" t="s">
+      <c r="C39" s="207" t="s">
         <v>415</v>
       </c>
       <c r="D39" s="204"/>
@@ -46955,7 +47166,7 @@
       <c r="B40" s="169" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="250" t="s">
+      <c r="C40" s="251" t="s">
         <v>416</v>
       </c>
       <c r="D40" s="204"/>
@@ -46997,7 +47208,7 @@
       <c r="B41" s="169" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="249" t="s">
+      <c r="C41" s="207" t="s">
         <v>417</v>
       </c>
       <c r="D41" s="204"/>
@@ -47039,7 +47250,7 @@
       <c r="B42" s="169" t="s">
         <v>142</v>
       </c>
-      <c r="C42" s="249" t="s">
+      <c r="C42" s="207" t="s">
         <v>105</v>
       </c>
       <c r="D42" s="204"/>
@@ -47081,7 +47292,7 @@
       <c r="B43" s="169" t="s">
         <v>163</v>
       </c>
-      <c r="C43" s="249" t="s">
+      <c r="C43" s="207" t="s">
         <v>418</v>
       </c>
       <c r="D43" s="204"/>
@@ -47123,7 +47334,7 @@
       <c r="B44" s="169" t="s">
         <v>165</v>
       </c>
-      <c r="C44" s="250" t="s">
+      <c r="C44" s="251" t="s">
         <v>419</v>
       </c>
       <c r="D44" s="204"/>
@@ -47165,7 +47376,7 @@
       <c r="B45" s="169" t="s">
         <v>167</v>
       </c>
-      <c r="C45" s="249" t="s">
+      <c r="C45" s="207" t="s">
         <v>420</v>
       </c>
       <c r="D45" s="204"/>
@@ -49887,6 +50098,17 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B1:AK1"/>
+    <mergeCell ref="C5:AK5"/>
+    <mergeCell ref="C42:AK42"/>
+    <mergeCell ref="C7:AK7"/>
+    <mergeCell ref="C14:AK14"/>
+    <mergeCell ref="C19:AK19"/>
+    <mergeCell ref="C13:AK13"/>
+    <mergeCell ref="C18:AK18"/>
+    <mergeCell ref="C3:AK3"/>
+    <mergeCell ref="C6:AK6"/>
+    <mergeCell ref="C15:AK15"/>
     <mergeCell ref="C45:AK45"/>
     <mergeCell ref="C4:AK4"/>
     <mergeCell ref="C16:AK16"/>
@@ -49902,17 +50124,6 @@
     <mergeCell ref="C39:AK39"/>
     <mergeCell ref="C8:AK8"/>
     <mergeCell ref="C38:AK38"/>
-    <mergeCell ref="B1:AK1"/>
-    <mergeCell ref="C5:AK5"/>
-    <mergeCell ref="C42:AK42"/>
-    <mergeCell ref="C7:AK7"/>
-    <mergeCell ref="C14:AK14"/>
-    <mergeCell ref="C19:AK19"/>
-    <mergeCell ref="C13:AK13"/>
-    <mergeCell ref="C18:AK18"/>
-    <mergeCell ref="C3:AK3"/>
-    <mergeCell ref="C6:AK6"/>
-    <mergeCell ref="C15:AK15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49924,30 +50135,30 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="37" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="37" width="3.44140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="248" t="s">
+      <c r="B1" s="208" t="s">
         <v>427</v>
       </c>
       <c r="C1" s="204"/>
@@ -49991,7 +50202,7 @@
       <c r="B3" s="169" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="247">
+      <c r="C3" s="206">
         <v>162000</v>
       </c>
       <c r="D3" s="204"/>
@@ -50033,7 +50244,7 @@
       <c r="B4" s="169" t="s">
         <v>395</v>
       </c>
-      <c r="C4" s="247">
+      <c r="C4" s="206">
         <v>372177.7</v>
       </c>
       <c r="D4" s="204"/>
@@ -50075,7 +50286,7 @@
       <c r="B5" s="169" t="s">
         <v>428</v>
       </c>
-      <c r="C5" s="247">
+      <c r="C5" s="206">
         <v>112750</v>
       </c>
       <c r="D5" s="204"/>
@@ -50117,7 +50328,7 @@
       <c r="B6" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="247">
+      <c r="C6" s="206">
         <v>1000</v>
       </c>
       <c r="D6" s="204"/>
@@ -50159,7 +50370,7 @@
       <c r="B7" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="206">
         <v>45435</v>
       </c>
       <c r="D7" s="204"/>
@@ -50201,7 +50412,7 @@
       <c r="B8" s="169" t="s">
         <v>396</v>
       </c>
-      <c r="C8" s="247">
+      <c r="C8" s="206">
         <v>1372</v>
       </c>
       <c r="D8" s="204"/>
@@ -50243,7 +50454,7 @@
       <c r="B9" s="169" t="s">
         <v>397</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="206">
         <v>3194</v>
       </c>
       <c r="D9" s="204"/>
@@ -50285,7 +50496,7 @@
       <c r="B10" s="169" t="s">
         <v>399</v>
       </c>
-      <c r="C10" s="246">
+      <c r="C10" s="205">
         <v>697928.7</v>
       </c>
       <c r="D10" s="204"/>
@@ -50332,7 +50543,7 @@
       <c r="B13" s="169" t="s">
         <v>401</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="206">
         <v>138857.14000000001</v>
       </c>
       <c r="D13" s="204"/>
@@ -50374,7 +50585,7 @@
       <c r="B14" s="169" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="247">
+      <c r="C14" s="206">
         <v>319009.46000000002</v>
       </c>
       <c r="D14" s="204"/>
@@ -50416,7 +50627,7 @@
       <c r="B15" s="169" t="s">
         <v>430</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="206">
         <v>96643</v>
       </c>
       <c r="D15" s="204"/>
@@ -50458,7 +50669,7 @@
       <c r="B16" s="169" t="s">
         <v>403</v>
       </c>
-      <c r="C16" s="247">
+      <c r="C16" s="206">
         <v>1176</v>
       </c>
       <c r="D16" s="204"/>
@@ -50500,7 +50711,7 @@
       <c r="B17" s="169" t="s">
         <v>404</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="206">
         <v>2737.71</v>
       </c>
       <c r="D17" s="204"/>
@@ -50542,7 +50753,7 @@
       <c r="B18" s="169" t="s">
         <v>405</v>
       </c>
-      <c r="C18" s="247">
+      <c r="C18" s="206">
         <v>1000</v>
       </c>
       <c r="D18" s="204"/>
@@ -50584,7 +50795,7 @@
       <c r="B19" s="169" t="s">
         <v>406</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="206">
         <v>45435</v>
       </c>
       <c r="D19" s="204"/>
@@ -50626,7 +50837,7 @@
       <c r="B20" s="169" t="s">
         <v>407</v>
       </c>
-      <c r="C20" s="246">
+      <c r="C20" s="205">
         <v>604858.31000000006</v>
       </c>
       <c r="D20" s="204"/>
@@ -50708,7 +50919,7 @@
       <c r="B23" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="249" t="s">
+      <c r="C23" s="207" t="s">
         <v>67</v>
       </c>
       <c r="D23" s="204"/>
@@ -50750,7 +50961,7 @@
       <c r="B24" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="249" t="s">
+      <c r="C24" s="207" t="s">
         <v>432</v>
       </c>
       <c r="D24" s="204"/>
@@ -50792,7 +51003,7 @@
       <c r="B25" s="169" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="252" t="s">
+      <c r="C25" s="203" t="s">
         <v>433</v>
       </c>
       <c r="D25" s="204"/>
@@ -53839,13 +54050,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C25:AK25"/>
-    <mergeCell ref="C10:AK10"/>
-    <mergeCell ref="C9:AK9"/>
-    <mergeCell ref="C17:AK17"/>
-    <mergeCell ref="C23:AK23"/>
-    <mergeCell ref="C24:AK24"/>
-    <mergeCell ref="C15:AK15"/>
     <mergeCell ref="B1:AK1"/>
     <mergeCell ref="C5:AK5"/>
     <mergeCell ref="C14:AK14"/>
@@ -53859,6 +54063,13 @@
     <mergeCell ref="C18:AK18"/>
     <mergeCell ref="C3:AK3"/>
     <mergeCell ref="C6:AK6"/>
+    <mergeCell ref="C25:AK25"/>
+    <mergeCell ref="C10:AK10"/>
+    <mergeCell ref="C9:AK9"/>
+    <mergeCell ref="C17:AK17"/>
+    <mergeCell ref="C23:AK23"/>
+    <mergeCell ref="C24:AK24"/>
+    <mergeCell ref="C15:AK15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53870,27 +54081,27 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="26" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="26" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="248" t="s">
+      <c r="B1" s="208" t="s">
         <v>436</v>
       </c>
       <c r="C1" s="204"/>
@@ -53934,7 +54145,7 @@
       <c r="B3" s="169" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="247">
+      <c r="C3" s="206">
         <v>164500</v>
       </c>
       <c r="D3" s="204"/>
@@ -53976,7 +54187,7 @@
       <c r="B4" s="169" t="s">
         <v>395</v>
       </c>
-      <c r="C4" s="247">
+      <c r="C4" s="206">
         <v>364711.2</v>
       </c>
       <c r="D4" s="204"/>
@@ -54018,7 +54229,7 @@
       <c r="B5" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="247">
+      <c r="C5" s="206">
         <v>2000</v>
       </c>
       <c r="D5" s="204"/>
@@ -54060,7 +54271,7 @@
       <c r="B6" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="247">
+      <c r="C6" s="206">
         <v>37740</v>
       </c>
       <c r="D6" s="204"/>
@@ -54102,7 +54313,7 @@
       <c r="B7" s="169" t="s">
         <v>396</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="206">
         <v>772</v>
       </c>
       <c r="D7" s="204"/>
@@ -54144,7 +54355,7 @@
       <c r="B8" s="169" t="s">
         <v>397</v>
       </c>
-      <c r="C8" s="247">
+      <c r="C8" s="206">
         <v>0</v>
       </c>
       <c r="D8" s="204"/>
@@ -54186,7 +54397,7 @@
       <c r="B9" s="169" t="s">
         <v>398</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="206">
         <v>772</v>
       </c>
       <c r="D9" s="204"/>
@@ -54228,7 +54439,7 @@
       <c r="B10" s="169" t="s">
         <v>399</v>
       </c>
-      <c r="C10" s="246">
+      <c r="C10" s="205">
         <v>569723.19999999995</v>
       </c>
       <c r="D10" s="204"/>
@@ -54275,7 +54486,7 @@
       <c r="B13" s="169" t="s">
         <v>401</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="206">
         <v>141000</v>
       </c>
       <c r="D13" s="204"/>
@@ -54317,7 +54528,7 @@
       <c r="B14" s="169" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="247">
+      <c r="C14" s="206">
         <v>312609.59999999998</v>
       </c>
       <c r="D14" s="204"/>
@@ -54359,7 +54570,7 @@
       <c r="B15" s="169" t="s">
         <v>403</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="206">
         <v>661.71</v>
       </c>
       <c r="D15" s="204"/>
@@ -54401,7 +54612,7 @@
       <c r="B16" s="169" t="s">
         <v>404</v>
       </c>
-      <c r="C16" s="247">
+      <c r="C16" s="206">
         <v>0</v>
       </c>
       <c r="D16" s="204"/>
@@ -54443,7 +54654,7 @@
       <c r="B17" s="169" t="s">
         <v>405</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="206">
         <v>2000</v>
       </c>
       <c r="D17" s="204"/>
@@ -54485,7 +54696,7 @@
       <c r="B18" s="169" t="s">
         <v>406</v>
       </c>
-      <c r="C18" s="247">
+      <c r="C18" s="206">
         <v>37740</v>
       </c>
       <c r="D18" s="204"/>
@@ -54527,7 +54738,7 @@
       <c r="B19" s="169" t="s">
         <v>407</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="205">
         <v>494011.31</v>
       </c>
       <c r="D19" s="204"/>
@@ -54574,7 +54785,7 @@
       <c r="B22" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="251">
+      <c r="C22" s="252">
         <v>1</v>
       </c>
       <c r="D22" s="204"/>
@@ -54616,7 +54827,7 @@
       <c r="B23" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="251">
+      <c r="C23" s="252">
         <v>1</v>
       </c>
       <c r="D23" s="204"/>
@@ -54835,7 +55046,7 @@
       <c r="B38" s="169" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="249" t="s">
+      <c r="C38" s="207" t="s">
         <v>73</v>
       </c>
       <c r="D38" s="204"/>
@@ -54877,7 +55088,7 @@
       <c r="B39" s="169" t="s">
         <v>158</v>
       </c>
-      <c r="C39" s="249" t="s">
+      <c r="C39" s="207" t="s">
         <v>437</v>
       </c>
       <c r="D39" s="204"/>
@@ -54919,7 +55130,7 @@
       <c r="B40" s="169" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="250" t="s">
+      <c r="C40" s="251" t="s">
         <v>161</v>
       </c>
       <c r="D40" s="204"/>
@@ -54961,7 +55172,7 @@
       <c r="B41" s="169" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="249" t="s">
+      <c r="C41" s="207" t="s">
         <v>417</v>
       </c>
       <c r="D41" s="204"/>
@@ -55003,7 +55214,7 @@
       <c r="B42" s="169" t="s">
         <v>142</v>
       </c>
-      <c r="C42" s="249" t="s">
+      <c r="C42" s="207" t="s">
         <v>105</v>
       </c>
       <c r="D42" s="204"/>
@@ -55045,7 +55256,7 @@
       <c r="B43" s="169" t="s">
         <v>163</v>
       </c>
-      <c r="C43" s="249" t="s">
+      <c r="C43" s="207" t="s">
         <v>438</v>
       </c>
       <c r="D43" s="204"/>
@@ -55087,7 +55298,7 @@
       <c r="B44" s="169" t="s">
         <v>165</v>
       </c>
-      <c r="C44" s="250" t="s">
+      <c r="C44" s="251" t="s">
         <v>439</v>
       </c>
       <c r="D44" s="204"/>
@@ -55129,7 +55340,7 @@
       <c r="B45" s="169" t="s">
         <v>167</v>
       </c>
-      <c r="C45" s="249" t="s">
+      <c r="C45" s="207" t="s">
         <v>420</v>
       </c>
       <c r="D45" s="204"/>
@@ -57853,6 +58064,17 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B1:AK1"/>
+    <mergeCell ref="C5:AK5"/>
+    <mergeCell ref="C42:AK42"/>
+    <mergeCell ref="C7:AK7"/>
+    <mergeCell ref="C14:AK14"/>
+    <mergeCell ref="C19:AK19"/>
+    <mergeCell ref="C13:AK13"/>
+    <mergeCell ref="C18:AK18"/>
+    <mergeCell ref="C3:AK3"/>
+    <mergeCell ref="C6:AK6"/>
+    <mergeCell ref="C15:AK15"/>
     <mergeCell ref="C45:AK45"/>
     <mergeCell ref="C4:AK4"/>
     <mergeCell ref="C16:AK16"/>
@@ -57868,17 +58090,6 @@
     <mergeCell ref="C39:AK39"/>
     <mergeCell ref="C8:AK8"/>
     <mergeCell ref="C38:AK38"/>
-    <mergeCell ref="B1:AK1"/>
-    <mergeCell ref="C5:AK5"/>
-    <mergeCell ref="C42:AK42"/>
-    <mergeCell ref="C7:AK7"/>
-    <mergeCell ref="C14:AK14"/>
-    <mergeCell ref="C19:AK19"/>
-    <mergeCell ref="C13:AK13"/>
-    <mergeCell ref="C18:AK18"/>
-    <mergeCell ref="C3:AK3"/>
-    <mergeCell ref="C6:AK6"/>
-    <mergeCell ref="C15:AK15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57890,12 +58101,32 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="212" t="s">
         <v>71</v>
       </c>
       <c r="C1" s="204"/>
@@ -57934,7 +58165,7 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="214">
+      <c r="C3" s="216">
         <v>540488.80000000005</v>
       </c>
       <c r="D3" s="204"/>
@@ -57971,7 +58202,7 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="211">
+      <c r="C4" s="213">
         <v>145500</v>
       </c>
       <c r="D4" s="204"/>
@@ -58008,7 +58239,7 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="211">
+      <c r="C5" s="213">
         <v>394988.79999999999</v>
       </c>
       <c r="D5" s="204"/>
@@ -58046,7 +58277,7 @@
       <c r="B7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="213" t="s">
+      <c r="C7" s="215" t="s">
         <v>73</v>
       </c>
       <c r="D7" s="204"/>
@@ -58083,7 +58314,7 @@
       <c r="B8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="213" t="s">
+      <c r="C8" s="215" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="204"/>
@@ -60228,30 +60459,30 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="37" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="37" width="3.44140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="248" t="s">
+      <c r="B1" s="208" t="s">
         <v>441</v>
       </c>
       <c r="C1" s="204"/>
@@ -60295,7 +60526,7 @@
       <c r="B3" s="169" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="247">
+      <c r="C3" s="206">
         <v>164500</v>
       </c>
       <c r="D3" s="204"/>
@@ -60337,7 +60568,7 @@
       <c r="B4" s="169" t="s">
         <v>395</v>
       </c>
-      <c r="C4" s="247">
+      <c r="C4" s="206">
         <v>369445.2</v>
       </c>
       <c r="D4" s="204"/>
@@ -60379,7 +60610,7 @@
       <c r="B5" s="169" t="s">
         <v>428</v>
       </c>
-      <c r="C5" s="247">
+      <c r="C5" s="206">
         <v>43250</v>
       </c>
       <c r="D5" s="204"/>
@@ -60421,7 +60652,7 @@
       <c r="B6" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="247">
+      <c r="C6" s="206">
         <v>2000</v>
       </c>
       <c r="D6" s="204"/>
@@ -60463,7 +60694,7 @@
       <c r="B7" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="206">
         <v>37740</v>
       </c>
       <c r="D7" s="204"/>
@@ -60505,7 +60736,7 @@
       <c r="B8" s="169" t="s">
         <v>396</v>
       </c>
-      <c r="C8" s="247">
+      <c r="C8" s="206">
         <v>772</v>
       </c>
       <c r="D8" s="204"/>
@@ -60547,7 +60778,7 @@
       <c r="B9" s="169" t="s">
         <v>397</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="206">
         <v>0</v>
       </c>
       <c r="D9" s="204"/>
@@ -60589,7 +60820,7 @@
       <c r="B10" s="169" t="s">
         <v>399</v>
       </c>
-      <c r="C10" s="246">
+      <c r="C10" s="205">
         <v>617707.19999999995</v>
       </c>
       <c r="D10" s="204"/>
@@ -60636,7 +60867,7 @@
       <c r="B13" s="169" t="s">
         <v>401</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="206">
         <v>141000</v>
       </c>
       <c r="D13" s="204"/>
@@ -60678,7 +60909,7 @@
       <c r="B14" s="169" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="247">
+      <c r="C14" s="206">
         <v>316667.31</v>
       </c>
       <c r="D14" s="204"/>
@@ -60720,7 +60951,7 @@
       <c r="B15" s="169" t="s">
         <v>430</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="206">
         <v>37072</v>
       </c>
       <c r="D15" s="204"/>
@@ -60762,7 +60993,7 @@
       <c r="B16" s="169" t="s">
         <v>403</v>
       </c>
-      <c r="C16" s="247">
+      <c r="C16" s="206">
         <v>661.71</v>
       </c>
       <c r="D16" s="204"/>
@@ -60804,7 +61035,7 @@
       <c r="B17" s="169" t="s">
         <v>404</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="206">
         <v>0</v>
       </c>
       <c r="D17" s="204"/>
@@ -60846,7 +61077,7 @@
       <c r="B18" s="169" t="s">
         <v>405</v>
       </c>
-      <c r="C18" s="247">
+      <c r="C18" s="206">
         <v>2000</v>
       </c>
       <c r="D18" s="204"/>
@@ -60888,7 +61119,7 @@
       <c r="B19" s="169" t="s">
         <v>406</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="206">
         <v>37740</v>
       </c>
       <c r="D19" s="204"/>
@@ -60930,7 +61161,7 @@
       <c r="B20" s="169" t="s">
         <v>407</v>
       </c>
-      <c r="C20" s="246">
+      <c r="C20" s="205">
         <v>535141.03</v>
       </c>
       <c r="D20" s="204"/>
@@ -61012,7 +61243,7 @@
       <c r="B23" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="249" t="s">
+      <c r="C23" s="207" t="s">
         <v>67</v>
       </c>
       <c r="D23" s="204"/>
@@ -61054,7 +61285,7 @@
       <c r="B24" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="249" t="s">
+      <c r="C24" s="207" t="s">
         <v>442</v>
       </c>
       <c r="D24" s="204"/>
@@ -61096,7 +61327,7 @@
       <c r="B25" s="169" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="252" t="s">
+      <c r="C25" s="203" t="s">
         <v>443</v>
       </c>
       <c r="D25" s="204"/>
@@ -64143,13 +64374,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C25:AK25"/>
-    <mergeCell ref="C10:AK10"/>
-    <mergeCell ref="C9:AK9"/>
-    <mergeCell ref="C17:AK17"/>
-    <mergeCell ref="C23:AK23"/>
-    <mergeCell ref="C24:AK24"/>
-    <mergeCell ref="C15:AK15"/>
     <mergeCell ref="B1:AK1"/>
     <mergeCell ref="C5:AK5"/>
     <mergeCell ref="C14:AK14"/>
@@ -64163,6 +64387,13 @@
     <mergeCell ref="C18:AK18"/>
     <mergeCell ref="C3:AK3"/>
     <mergeCell ref="C6:AK6"/>
+    <mergeCell ref="C25:AK25"/>
+    <mergeCell ref="C10:AK10"/>
+    <mergeCell ref="C9:AK9"/>
+    <mergeCell ref="C17:AK17"/>
+    <mergeCell ref="C23:AK23"/>
+    <mergeCell ref="C24:AK24"/>
+    <mergeCell ref="C15:AK15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -64174,13 +64405,26 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="212" t="s">
         <v>81</v>
       </c>
       <c r="C1" s="204"/>
@@ -64219,7 +64463,7 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="211">
+      <c r="C3" s="213">
         <v>145500</v>
       </c>
       <c r="D3" s="204"/>
@@ -64256,7 +64500,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="211">
+      <c r="C4" s="213">
         <v>401114.8</v>
       </c>
       <c r="D4" s="204"/>
@@ -64293,7 +64537,7 @@
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="211">
+      <c r="C5" s="213">
         <v>27500</v>
       </c>
       <c r="D5" s="204"/>
@@ -64330,7 +64574,7 @@
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="214">
+      <c r="C6" s="216">
         <v>574114.80000000005</v>
       </c>
       <c r="D6" s="204"/>
@@ -64403,7 +64647,7 @@
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="213" t="s">
+      <c r="C9" s="215" t="s">
         <v>82</v>
       </c>
       <c r="D9" s="204"/>
@@ -64440,7 +64684,7 @@
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="213" t="s">
+      <c r="C10" s="215" t="s">
         <v>83</v>
       </c>
       <c r="D10" s="204"/>
@@ -64477,7 +64721,7 @@
       <c r="B11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="216" t="s">
+      <c r="C11" s="217" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="204"/>
@@ -66870,12 +67114,29 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="212" t="s">
         <v>99</v>
       </c>
       <c r="C1" s="204"/>
@@ -66914,7 +67175,7 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="211">
+      <c r="C3" s="213">
         <v>145500</v>
       </c>
       <c r="D3" s="204"/>
@@ -66951,7 +67212,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="211">
+      <c r="C4" s="213">
         <v>369326.8</v>
       </c>
       <c r="D4" s="204"/>
@@ -66988,7 +67249,7 @@
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="211">
+      <c r="C5" s="213">
         <v>132</v>
       </c>
       <c r="D5" s="204"/>
@@ -67025,7 +67286,7 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="211">
+      <c r="C6" s="213">
         <v>6312</v>
       </c>
       <c r="D6" s="204"/>
@@ -67062,7 +67323,7 @@
       <c r="B7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="211">
+      <c r="C7" s="213">
         <v>6444</v>
       </c>
       <c r="D7" s="204"/>
@@ -67099,7 +67360,7 @@
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="214">
+      <c r="C8" s="216">
         <v>521270.8</v>
       </c>
       <c r="D8" s="204"/>
@@ -67137,7 +67398,7 @@
       <c r="B10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="213" t="s">
+      <c r="C10" s="215" t="s">
         <v>73</v>
       </c>
       <c r="D10" s="204"/>
@@ -67174,7 +67435,7 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="213" t="s">
+      <c r="C11" s="215" t="s">
         <v>103</v>
       </c>
       <c r="D11" s="204"/>
@@ -67211,7 +67472,7 @@
       <c r="B12" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="213" t="s">
+      <c r="C12" s="215" t="s">
         <v>105</v>
       </c>
       <c r="D12" s="204"/>
@@ -67248,7 +67509,7 @@
       <c r="B13" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="213" t="s">
+      <c r="C13" s="215" t="s">
         <v>107</v>
       </c>
       <c r="D13" s="204"/>
@@ -69707,7 +69968,7 @@
       <c r="B3" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="217">
+      <c r="C3" s="220">
         <v>155500</v>
       </c>
       <c r="D3" s="204"/>
@@ -69744,7 +70005,7 @@
       <c r="B4" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="217">
+      <c r="C4" s="220">
         <v>382825</v>
       </c>
       <c r="D4" s="204"/>
@@ -69781,7 +70042,7 @@
       <c r="B5" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="217">
+      <c r="C5" s="220">
         <v>442</v>
       </c>
       <c r="D5" s="204"/>
@@ -69818,7 +70079,7 @@
       <c r="B6" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="217">
+      <c r="C6" s="220">
         <v>0</v>
       </c>
       <c r="D6" s="204"/>
@@ -69855,7 +70116,7 @@
       <c r="B7" s="112" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="217">
+      <c r="C7" s="220">
         <v>442</v>
       </c>
       <c r="D7" s="204"/>
@@ -69892,7 +70153,7 @@
       <c r="B8" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="217">
+      <c r="C8" s="220">
         <v>0</v>
       </c>
       <c r="D8" s="204"/>
@@ -69929,7 +70190,7 @@
       <c r="B9" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="220">
+      <c r="C9" s="221">
         <v>538767</v>
       </c>
       <c r="D9" s="204"/>
@@ -72332,7 +72593,7 @@
       <c r="B3" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="221">
+      <c r="C3" s="223">
         <v>145500</v>
       </c>
       <c r="D3" s="204"/>
@@ -72369,7 +72630,7 @@
       <c r="B4" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="221">
+      <c r="C4" s="223">
         <v>375608.8</v>
       </c>
       <c r="D4" s="204"/>
@@ -72406,7 +72667,7 @@
       <c r="B5" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="221">
+      <c r="C5" s="223">
         <v>132</v>
       </c>
       <c r="D5" s="204"/>
@@ -72443,7 +72704,7 @@
       <c r="B6" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="221">
+      <c r="C6" s="223">
         <v>6312</v>
       </c>
       <c r="D6" s="204"/>
@@ -72480,7 +72741,7 @@
       <c r="B7" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="221">
+      <c r="C7" s="223">
         <v>34000</v>
       </c>
       <c r="D7" s="204"/>
@@ -72517,7 +72778,7 @@
       <c r="B8" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="222">
+      <c r="C8" s="224">
         <v>561552.80000000005</v>
       </c>
       <c r="D8" s="204"/>
@@ -72554,7 +72815,7 @@
       <c r="B9" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="221">
+      <c r="C9" s="223">
         <v>521270.8</v>
       </c>
       <c r="D9" s="204"/>
@@ -72591,7 +72852,7 @@
       <c r="B10" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="221">
+      <c r="C10" s="223">
         <v>40282</v>
       </c>
       <c r="D10" s="204"/>
@@ -72738,7 +72999,7 @@
       <c r="B15" s="112" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="223" t="s">
+      <c r="C15" s="222" t="s">
         <v>129</v>
       </c>
       <c r="D15" s="204"/>
@@ -75027,12 +75288,22 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="21" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="212" t="s">
         <v>134</v>
       </c>
       <c r="C1" s="204"/>
@@ -75071,7 +75342,7 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="211">
+      <c r="C3" s="213">
         <v>143000</v>
       </c>
       <c r="D3" s="204"/>
@@ -75108,7 +75379,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="211">
+      <c r="C4" s="213">
         <v>364253.3</v>
       </c>
       <c r="D4" s="204"/>
@@ -75145,7 +75416,7 @@
       <c r="B5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="211">
+      <c r="C5" s="213">
         <v>1020</v>
       </c>
       <c r="D5" s="204"/>
@@ -75182,7 +75453,7 @@
       <c r="B6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="211">
+      <c r="C6" s="213">
         <v>12450</v>
       </c>
       <c r="D6" s="204"/>
@@ -75219,7 +75490,7 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="214">
+      <c r="C7" s="216">
         <v>520723.3</v>
       </c>
       <c r="D7" s="204"/>
@@ -75257,7 +75528,7 @@
       <c r="B9" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="213" t="s">
+      <c r="C9" s="215" t="s">
         <v>73</v>
       </c>
       <c r="D9" s="204"/>
@@ -75294,7 +75565,7 @@
       <c r="B10" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="213" t="s">
+      <c r="C10" s="215" t="s">
         <v>139</v>
       </c>
       <c r="D10" s="204"/>
@@ -75331,7 +75602,7 @@
       <c r="B11" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C11" s="224" t="s">
+      <c r="C11" s="225" t="s">
         <v>141</v>
       </c>
       <c r="D11" s="204"/>
@@ -75368,7 +75639,7 @@
       <c r="B12" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="213" t="s">
+      <c r="C12" s="215" t="s">
         <v>105</v>
       </c>
       <c r="D12" s="204"/>
@@ -75405,7 +75676,7 @@
       <c r="B13" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="213" t="s">
+      <c r="C13" s="215" t="s">
         <v>144</v>
       </c>
       <c r="D13" s="204"/>
@@ -75442,7 +75713,7 @@
       <c r="B14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="224" t="s">
+      <c r="C14" s="225" t="s">
         <v>146</v>
       </c>
       <c r="D14" s="204"/>
@@ -77585,12 +77856,20 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="33" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="21" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="228" t="s">
+      <c r="B1" s="227" t="s">
         <v>148</v>
       </c>
       <c r="C1" s="204"/>
@@ -77629,7 +77908,7 @@
       <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="225">
+      <c r="C3" s="229">
         <v>143000</v>
       </c>
       <c r="D3" s="204"/>
@@ -77666,7 +77945,7 @@
       <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="225">
+      <c r="C4" s="229">
         <v>370457.3</v>
       </c>
       <c r="D4" s="204"/>
@@ -77703,7 +77982,7 @@
       <c r="B5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="225">
+      <c r="C5" s="229">
         <v>30750</v>
       </c>
       <c r="D5" s="204"/>
@@ -77740,7 +78019,7 @@
       <c r="B6" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="225">
+      <c r="C6" s="229">
         <v>1020</v>
       </c>
       <c r="D6" s="204"/>
@@ -77777,7 +78056,7 @@
       <c r="B7" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="225">
+      <c r="C7" s="229">
         <v>12450</v>
       </c>
       <c r="D7" s="204"/>
@@ -77814,7 +78093,7 @@
       <c r="B8" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="226">
+      <c r="C8" s="231">
         <v>557677.30000000005</v>
       </c>
       <c r="D8" s="204"/>
@@ -77851,7 +78130,7 @@
       <c r="B9" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="225">
+      <c r="C9" s="229">
         <v>520723.3</v>
       </c>
       <c r="D9" s="204"/>
@@ -77888,7 +78167,7 @@
       <c r="B10" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="229">
+      <c r="C10" s="228">
         <v>36954</v>
       </c>
       <c r="D10" s="204"/>
@@ -78035,7 +78314,7 @@
       <c r="B15" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="227" t="s">
+      <c r="C15" s="226" t="s">
         <v>152</v>
       </c>
       <c r="D15" s="204"/>
